--- a/mentor data/hadier 5-talaria-adapted.xlsx
+++ b/mentor data/hadier 5-talaria-adapted.xlsx
@@ -1304,7 +1304,7 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28255, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/jRxeSy9V/", "exitScreenshotUrl": "https://www.tradingview.com/x/jRxeSy9V/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28255, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/jRxeSy9V/", "exitScreenshotUrl": "https://www.tradingview.com/x/jRxeSy9V/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2301.86, "sourceLowPrice": 2294.9}</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK2" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL2" t="n">
-        <v>1782553984118</v>
+        <v>1782575585776</v>
       </c>
       <c r="BM2" t="n">
         <v>2289.809</v>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28199, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/PIEyLfQh/", "exitScreenshotUrl": "https://www.tradingview.com/x/W0rZm9XJ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28199, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/PIEyLfQh/", "exitScreenshotUrl": "https://www.tradingview.com/x/W0rZm9XJ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2316.46, "sourceLowPrice": 2313.7}</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK3" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL3" t="n">
-        <v>1782553984118</v>
+        <v>1782575585777</v>
       </c>
       <c r="BM3" t="n">
         <v>2318.202</v>
@@ -2085,12 +2085,12 @@
       </c>
       <c r="DQ3" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR3" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS3" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28182, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/UAMJBO4F/", "exitScreenshotUrl": "https://www.tradingview.com/x/pVNahenz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28182, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/UAMJBO4F/", "exitScreenshotUrl": "https://www.tradingview.com/x/pVNahenz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2315.18, "sourceLowPrice": 2310.5}</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -2401,13 +2401,13 @@
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK4" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL4" t="n">
-        <v>1782553984119</v>
+        <v>1782575585777</v>
       </c>
       <c r="BM4" t="n">
         <v>2316.26</v>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="DQ4" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR4" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS4" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28234, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/b0romhzm/", "exitScreenshotUrl": "https://www.tradingview.com/x/3hIitC5V/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28234, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/b0romhzm/", "exitScreenshotUrl": "https://www.tradingview.com/x/3hIitC5V/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2302.51, "sourceLowPrice": 2293.018}</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -2925,13 +2925,13 @@
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK5" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL5" t="n">
-        <v>1782553984119</v>
+        <v>1782575585778</v>
       </c>
       <c r="BM5" t="n">
         <v>2302.938</v>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="DQ5" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR5" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS5" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 18585, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/WfIEhctn/", "exitScreenshotUrl": "https://www.tradingview.com/x/csXLFkS4/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 18585, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/WfIEhctn/", "exitScreenshotUrl": "https://www.tradingview.com/x/csXLFkS4/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2300.52, "sourceLowPrice": 2293.018}</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -3449,13 +3449,13 @@
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK6" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL6" t="n">
-        <v>1782553984119</v>
+        <v>1782575585778</v>
       </c>
       <c r="BM6" t="n">
         <v>2299.357</v>
@@ -3657,12 +3657,12 @@
       </c>
       <c r="DQ6" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR6" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS6" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28253, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qfF2m4SA/", "exitScreenshotUrl": "https://www.tradingview.com/x/atW9ItK5/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28253, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qfF2m4SA/", "exitScreenshotUrl": "https://www.tradingview.com/x/atW9ItK5/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2309.287, "sourceLowPrice": 2302.385}</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -3973,13 +3973,13 @@
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK7" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL7" t="n">
-        <v>1782553984119</v>
+        <v>1782575585779</v>
       </c>
       <c r="BM7" t="n">
         <v>2300.332</v>
@@ -4181,12 +4181,12 @@
       </c>
       <c r="DQ7" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR7" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS7" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 18921, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ukXfHVE6/", "exitScreenshotUrl": "https://www.tradingview.com/x/LkazmjPv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 18921, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ukXfHVE6/", "exitScreenshotUrl": "https://www.tradingview.com/x/LkazmjPv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2310.46, "sourceLowPrice": 2304.3}</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -4497,13 +4497,13 @@
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK8" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL8" t="n">
-        <v>1782553984119</v>
+        <v>1782575585779</v>
       </c>
       <c r="BM8" t="n">
         <v>2304.719</v>
@@ -4705,12 +4705,12 @@
       </c>
       <c r="DQ8" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR8" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS8" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 20122, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Hus5JQfv/", "exitScreenshotUrl": "https://www.tradingview.com/x/qOkEoVR0/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 20122, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Hus5JQfv/", "exitScreenshotUrl": "https://www.tradingview.com/x/qOkEoVR0/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2306.98, "sourceLowPrice": 2302.0}</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK9" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL9" t="n">
-        <v>1782553984119</v>
+        <v>1782575585779</v>
       </c>
       <c r="BM9" t="n">
         <v>2302.805</v>
@@ -5229,12 +5229,12 @@
       </c>
       <c r="DQ9" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR9" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS9" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28202, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AtJcWBS2/", "exitScreenshotUrl": "https://www.tradingview.com/x/8uZWmH5T/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28202, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AtJcWBS2/", "exitScreenshotUrl": "https://www.tradingview.com/x/8uZWmH5T/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2311.1, "sourceLowPrice": 2306.5}</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -5545,13 +5545,13 @@
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK10" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL10" t="n">
-        <v>1782553984120</v>
+        <v>1782575585780</v>
       </c>
       <c r="BM10" t="n">
         <v>2312.001</v>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="DQ10" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR10" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS10" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 20169, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/YYiJB7mR/", "exitScreenshotUrl": "https://www.tradingview.com/x/mU7a5ueZ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 20169, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/YYiJB7mR/", "exitScreenshotUrl": "https://www.tradingview.com/x/mU7a5ueZ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2308.14, "sourceLowPrice": 2304.1}</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -6069,13 +6069,13 @@
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK11" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL11" t="n">
-        <v>1782553984120</v>
+        <v>1782575585780</v>
       </c>
       <c r="BM11" t="n">
         <v>2309.928</v>
@@ -6277,12 +6277,12 @@
       </c>
       <c r="DQ11" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR11" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS11" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28254, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/c3LwRxSZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/0PbXEiKd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28254, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/c3LwRxSZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/0PbXEiKd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2307.24, "sourceLowPrice": 2302.914}</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -6593,13 +6593,13 @@
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK12" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL12" t="n">
-        <v>1782553984120</v>
+        <v>1782575585781</v>
       </c>
       <c r="BM12" t="n">
         <v>2308.041</v>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="DQ12" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR12" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS12" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28204, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/8iNqHntm/", "exitScreenshotUrl": "https://www.tradingview.com/x/V7JCHdts/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28204, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/8iNqHntm/", "exitScreenshotUrl": "https://www.tradingview.com/x/V7JCHdts/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2302.34, "sourceLowPrice": 2297.6}</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -7117,13 +7117,13 @@
         </is>
       </c>
       <c r="BJ13" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK13" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL13" t="n">
-        <v>1782553984121</v>
+        <v>1782575585781</v>
       </c>
       <c r="BM13" t="n">
         <v>2297.26</v>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="DQ13" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR13" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS13" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28267, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/lXVzZDyF/", "exitScreenshotUrl": "https://www.tradingview.com/x/pu5BtGwk/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28267, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/lXVzZDyF/", "exitScreenshotUrl": "https://www.tradingview.com/x/pu5BtGwk/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2323.69, "sourceLowPrice": 2319.395}</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -7641,13 +7641,13 @@
         </is>
       </c>
       <c r="BJ14" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK14" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL14" t="n">
-        <v>1782553984121</v>
+        <v>1782575585781</v>
       </c>
       <c r="BM14" t="n">
         <v>2322.981</v>
@@ -7849,12 +7849,12 @@
       </c>
       <c r="DQ14" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR14" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS14" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28256, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/TfuaYUaO/", "exitScreenshotUrl": "https://www.tradingview.com/x/IOF3W1Qc/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28256, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/TfuaYUaO/", "exitScreenshotUrl": "https://www.tradingview.com/x/IOF3W1Qc/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2326.191, "sourceLowPrice": 2318.535}</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -8165,13 +8165,13 @@
         </is>
       </c>
       <c r="BJ15" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK15" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL15" t="n">
-        <v>1782553984121</v>
+        <v>1782575585782</v>
       </c>
       <c r="BM15" t="n">
         <v>2325.153</v>
@@ -8373,12 +8373,12 @@
       </c>
       <c r="DQ15" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR15" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS15" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28268, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/mClIVHU6/", "exitScreenshotUrl": "https://www.tradingview.com/x/rDz3tNzq/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28268, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/mClIVHU6/", "exitScreenshotUrl": "https://www.tradingview.com/x/rDz3tNzq/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2319.16, "sourceLowPrice": 2312.7}</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -8689,13 +8689,13 @@
         </is>
       </c>
       <c r="BJ16" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK16" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL16" t="n">
-        <v>1782553984121</v>
+        <v>1782575585782</v>
       </c>
       <c r="BM16" t="n">
         <v>2320.167</v>
@@ -8897,12 +8897,12 @@
       </c>
       <c r="DQ16" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR16" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS16" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28206, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/TTKcNwhr/", "exitScreenshotUrl": "https://www.tradingview.com/x/TpJoXp6K/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28206, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/TTKcNwhr/", "exitScreenshotUrl": "https://www.tradingview.com/x/TpJoXp6K/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2316.112, "sourceLowPrice": 2312.4}</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -9213,13 +9213,13 @@
         </is>
       </c>
       <c r="BJ17" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK17" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL17" t="n">
-        <v>1782553984121</v>
+        <v>1782575585783</v>
       </c>
       <c r="BM17" t="n">
         <v>2316.112</v>
@@ -9421,12 +9421,12 @@
       </c>
       <c r="DQ17" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR17" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS17" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 20790, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9AzlOCXX/", "exitScreenshotUrl": "https://www.tradingview.com/x/fFLGT4pD/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 20790, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9AzlOCXX/", "exitScreenshotUrl": "https://www.tradingview.com/x/fFLGT4pD/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2321.14, "sourceLowPrice": 2317.371}</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -9737,13 +9737,13 @@
         </is>
       </c>
       <c r="BJ18" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK18" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL18" t="n">
-        <v>1782553984121</v>
+        <v>1782575585783</v>
       </c>
       <c r="BM18" t="n">
         <v>2318.24</v>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="DQ18" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR18" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS18" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 21967, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/vOAg15bN/", "exitScreenshotUrl": "https://www.tradingview.com/x/DTGSbQGd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 21967, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/vOAg15bN/", "exitScreenshotUrl": "https://www.tradingview.com/x/DTGSbQGd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2313.06, "sourceLowPrice": 2308.7}</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -10261,13 +10261,13 @@
         </is>
       </c>
       <c r="BJ19" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK19" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL19" t="n">
-        <v>1782553984122</v>
+        <v>1782575585784</v>
       </c>
       <c r="BM19" t="n">
         <v>2313.328</v>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="DQ19" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR19" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS19" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28280, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/bZFIl2Qo/", "exitScreenshotUrl": "https://www.tradingview.com/x/r8u9CKtk/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28280, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/bZFIl2Qo/", "exitScreenshotUrl": "https://www.tradingview.com/x/r8u9CKtk/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2337.67, "sourceLowPrice": 2332.958}</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
@@ -10785,13 +10785,13 @@
         </is>
       </c>
       <c r="BJ20" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK20" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL20" t="n">
-        <v>1782553984122</v>
+        <v>1782575585784</v>
       </c>
       <c r="BM20" t="n">
         <v>2330.21</v>
@@ -10993,12 +10993,12 @@
       </c>
       <c r="DQ20" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR20" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS20" t="inlineStr">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 22894, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/PK3dh2ZJ/", "exitScreenshotUrl": "https://www.tradingview.com/x/bW4InguD/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 22894, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/PK3dh2ZJ/", "exitScreenshotUrl": "https://www.tradingview.com/x/bW4InguD/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2372.18, "sourceLowPrice": 2367.1}</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
@@ -11309,13 +11309,13 @@
         </is>
       </c>
       <c r="BJ21" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK21" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL21" t="n">
-        <v>1782553984122</v>
+        <v>1782575585785</v>
       </c>
       <c r="BM21" t="n">
         <v>2366.471</v>
@@ -11517,12 +11517,12 @@
       </c>
       <c r="DQ21" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR21" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS21" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28291, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ORBKdj9n/", "exitScreenshotUrl": "https://www.tradingview.com/x/VrYgZMka/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28291, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ORBKdj9n/", "exitScreenshotUrl": "https://www.tradingview.com/x/VrYgZMka/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2363.241, "sourceLowPrice": 2357.5}</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="BJ22" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK22" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL22" t="n">
-        <v>1782553984122</v>
+        <v>1782575585785</v>
       </c>
       <c r="BM22" t="n">
         <v>2366.151</v>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="DQ22" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR22" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS22" t="inlineStr">
@@ -12308,7 +12308,7 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28275, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/pXXTLeLm/", "exitScreenshotUrl": "https://www.tradingview.com/x/qiPyN0UP/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28275, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/pXXTLeLm/", "exitScreenshotUrl": "https://www.tradingview.com/x/qiPyN0UP/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2346.219, "sourceLowPrice": 2341.6}</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
@@ -12357,13 +12357,13 @@
         </is>
       </c>
       <c r="BJ23" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK23" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL23" t="n">
-        <v>1782553984122</v>
+        <v>1782575585785</v>
       </c>
       <c r="BM23" t="n">
         <v>2348.369</v>
@@ -12565,12 +12565,12 @@
       </c>
       <c r="DQ23" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR23" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS23" t="inlineStr">
@@ -12832,7 +12832,7 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28282, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/pXz2il84/", "exitScreenshotUrl": "https://www.tradingview.com/x/GMPdgWPs/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28282, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/pXz2il84/", "exitScreenshotUrl": "https://www.tradingview.com/x/GMPdgWPs/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2337.54, "sourceLowPrice": 2332.695}</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
@@ -12881,13 +12881,13 @@
         </is>
       </c>
       <c r="BJ24" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK24" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL24" t="n">
-        <v>1782553984122</v>
+        <v>1782575585786</v>
       </c>
       <c r="BM24" t="n">
         <v>2337.043</v>
@@ -13089,12 +13089,12 @@
       </c>
       <c r="DQ24" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR24" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS24" t="inlineStr">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28294, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/hCST1I6h/", "exitScreenshotUrl": "https://www.tradingview.com/x/6NCvuodm/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28294, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/hCST1I6h/", "exitScreenshotUrl": "https://www.tradingview.com/x/6NCvuodm/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2343.64, "sourceLowPrice": 2340.0}</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
@@ -13405,13 +13405,13 @@
         </is>
       </c>
       <c r="BJ25" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK25" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL25" t="n">
-        <v>1782553984123</v>
+        <v>1782575585786</v>
       </c>
       <c r="BM25" t="n">
         <v>2338.4</v>
@@ -13613,12 +13613,12 @@
       </c>
       <c r="DQ25" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR25" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS25" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28281, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/y7dwa5mf/", "exitScreenshotUrl": "https://www.tradingview.com/x/GMu636ia/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28281, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/y7dwa5mf/", "exitScreenshotUrl": "https://www.tradingview.com/x/GMu636ia/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2355.591, "sourceLowPrice": 2346.1}</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
@@ -13929,13 +13929,13 @@
         </is>
       </c>
       <c r="BJ26" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK26" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL26" t="n">
-        <v>1782553984123</v>
+        <v>1782575585786</v>
       </c>
       <c r="BM26" t="n">
         <v>2349.026</v>
@@ -14137,12 +14137,12 @@
       </c>
       <c r="DQ26" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR26" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS26" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28319, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/nzdOGiVZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/Yl8oNeA6/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28319, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/nzdOGiVZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/Yl8oNeA6/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2369.71, "sourceLowPrice": 2364.4}</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
@@ -14453,13 +14453,13 @@
         </is>
       </c>
       <c r="BJ27" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK27" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL27" t="n">
-        <v>1782553984123</v>
+        <v>1782575585787</v>
       </c>
       <c r="BM27" t="n">
         <v>2363.004</v>
@@ -14661,12 +14661,12 @@
       </c>
       <c r="DQ27" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR27" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS27" t="inlineStr">
@@ -14928,7 +14928,7 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28284, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/32Rd6KK1/", "exitScreenshotUrl": "https://www.tradingview.com/x/fGAzHaWE/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28284, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/32Rd6KK1/", "exitScreenshotUrl": "https://www.tradingview.com/x/fGAzHaWE/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2374.26, "sourceLowPrice": 2369.9}</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
@@ -14977,13 +14977,13 @@
         </is>
       </c>
       <c r="BJ28" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK28" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL28" t="n">
-        <v>1782553984123</v>
+        <v>1782575585787</v>
       </c>
       <c r="BM28" t="n">
         <v>2370.221</v>
@@ -15185,12 +15185,12 @@
       </c>
       <c r="DQ28" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR28" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS28" t="inlineStr">
@@ -15452,7 +15452,7 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28320, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/tKKMkLiP/", "exitScreenshotUrl": "https://www.tradingview.com/x/x8unseOM/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28320, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/tKKMkLiP/", "exitScreenshotUrl": "https://www.tradingview.com/x/x8unseOM/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2388.71, "sourceLowPrice": 2381.945}</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
@@ -15501,13 +15501,13 @@
         </is>
       </c>
       <c r="BJ29" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK29" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL29" t="n">
-        <v>1782553984123</v>
+        <v>1782575585787</v>
       </c>
       <c r="BM29" t="n">
         <v>2380.714</v>
@@ -15709,12 +15709,12 @@
       </c>
       <c r="DQ29" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR29" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS29" t="inlineStr">
@@ -15976,7 +15976,7 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 10422, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/TgJ4YuPz/", "exitScreenshotUrl": "https://www.tradingview.com/x/6VnZ6rzy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 10422, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/TgJ4YuPz/", "exitScreenshotUrl": "https://www.tradingview.com/x/6VnZ6rzy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2388.13, "sourceLowPrice": 2385.3}</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
@@ -16025,13 +16025,13 @@
         </is>
       </c>
       <c r="BJ30" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK30" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL30" t="n">
-        <v>1782553984123</v>
+        <v>1782575585788</v>
       </c>
       <c r="BM30" t="n">
         <v>2389.744</v>
@@ -16233,12 +16233,12 @@
       </c>
       <c r="DQ30" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR30" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS30" t="inlineStr">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 25102, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/zibMbKss/", "exitScreenshotUrl": "https://www.tradingview.com/x/FPBkTWDv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 25102, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/zibMbKss/", "exitScreenshotUrl": "https://www.tradingview.com/x/FPBkTWDv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2382.37, "sourceLowPrice": 2379.025}</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
@@ -16549,13 +16549,13 @@
         </is>
       </c>
       <c r="BJ31" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK31" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL31" t="n">
-        <v>1782553984124</v>
+        <v>1782575585788</v>
       </c>
       <c r="BM31" t="n">
         <v>2379.025</v>
@@ -16757,12 +16757,12 @@
       </c>
       <c r="DQ31" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR31" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS31" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28285, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ICDiOLLn/", "exitScreenshotUrl": "https://www.tradingview.com/x/HwOj1Eue/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28285, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ICDiOLLn/", "exitScreenshotUrl": "https://www.tradingview.com/x/HwOj1Eue/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2383.801, "sourceLowPrice": 2379.6}</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
@@ -17073,13 +17073,13 @@
         </is>
       </c>
       <c r="BJ32" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK32" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL32" t="n">
-        <v>1782553984124</v>
+        <v>1782575585789</v>
       </c>
       <c r="BM32" t="n">
         <v>2380.195</v>
@@ -17281,12 +17281,12 @@
       </c>
       <c r="DQ32" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR32" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS32" t="inlineStr">
@@ -17548,7 +17548,7 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28343, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/L5xp9Up9/", "exitScreenshotUrl": "https://www.tradingview.com/x/HAPE9Aeg/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28343, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/L5xp9Up9/", "exitScreenshotUrl": "https://www.tradingview.com/x/HAPE9Aeg/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2384.65, "sourceLowPrice": 2381.7}</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
@@ -17597,13 +17597,13 @@
         </is>
       </c>
       <c r="BJ33" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK33" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL33" t="n">
-        <v>1782553984124</v>
+        <v>1782575585789</v>
       </c>
       <c r="BM33" t="n">
         <v>2384.366</v>
@@ -17805,12 +17805,12 @@
       </c>
       <c r="DQ33" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR33" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS33" t="inlineStr">
@@ -18072,7 +18072,7 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28303, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/uK3Yslei/", "exitScreenshotUrl": "https://www.tradingview.com/x/HxzjypGM/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28303, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/uK3Yslei/", "exitScreenshotUrl": "https://www.tradingview.com/x/HxzjypGM/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2385.5, "sourceLowPrice": 2381.1}</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
@@ -18121,13 +18121,13 @@
         </is>
       </c>
       <c r="BJ34" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK34" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL34" t="n">
-        <v>1782553984124</v>
+        <v>1782575585789</v>
       </c>
       <c r="BM34" t="n">
         <v>2383.578</v>
@@ -18329,12 +18329,12 @@
       </c>
       <c r="DQ34" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR34" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS34" t="inlineStr">
@@ -18596,7 +18596,7 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28344, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MBCGmRhD/", "exitScreenshotUrl": "https://www.tradingview.com/x/NNnEgkpc/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28344, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MBCGmRhD/", "exitScreenshotUrl": "https://www.tradingview.com/x/NNnEgkpc/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2409.62, "sourceLowPrice": 2403.123}</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
@@ -18645,13 +18645,13 @@
         </is>
       </c>
       <c r="BJ35" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK35" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL35" t="n">
-        <v>1782553984124</v>
+        <v>1782575585790</v>
       </c>
       <c r="BM35" t="n">
         <v>2401.61</v>
@@ -18853,12 +18853,12 @@
       </c>
       <c r="DQ35" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR35" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS35" t="inlineStr">
@@ -19120,7 +19120,7 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28326, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/iUr4W7dl/", "exitScreenshotUrl": "https://www.tradingview.com/x/cbv2i0tm/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28326, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/iUr4W7dl/", "exitScreenshotUrl": "https://www.tradingview.com/x/cbv2i0tm/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2414.938, "sourceLowPrice": 2410.495}</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
@@ -19169,13 +19169,13 @@
         </is>
       </c>
       <c r="BJ36" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK36" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL36" t="n">
-        <v>1782553984124</v>
+        <v>1782575585790</v>
       </c>
       <c r="BM36" t="n">
         <v>2411.41</v>
@@ -19377,12 +19377,12 @@
       </c>
       <c r="DQ36" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR36" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS36" t="inlineStr">
@@ -19644,7 +19644,7 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28347, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/kGjra2LJ/", "exitScreenshotUrl": "https://www.tradingview.com/x/MrgHQkXb/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28347, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/kGjra2LJ/", "exitScreenshotUrl": "https://www.tradingview.com/x/MrgHQkXb/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2426.96, "sourceLowPrice": 2421.3}</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
@@ -19693,13 +19693,13 @@
         </is>
       </c>
       <c r="BJ37" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK37" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL37" t="n">
-        <v>1782553984124</v>
+        <v>1782575585791</v>
       </c>
       <c r="BM37" t="n">
         <v>2419.664</v>
@@ -19901,12 +19901,12 @@
       </c>
       <c r="DQ37" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR37" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS37" t="inlineStr">
@@ -20168,7 +20168,7 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28305, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/bmDKObH1/", "exitScreenshotUrl": "https://www.tradingview.com/x/AD9ws3Du/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28305, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/bmDKObH1/", "exitScreenshotUrl": "https://www.tradingview.com/x/AD9ws3Du/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2428.13, "sourceLowPrice": 2423.9}</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
@@ -20217,13 +20217,13 @@
         </is>
       </c>
       <c r="BJ38" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK38" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL38" t="n">
-        <v>1782553984125</v>
+        <v>1782575585791</v>
       </c>
       <c r="BM38" t="n">
         <v>2424.568</v>
@@ -20425,12 +20425,12 @@
       </c>
       <c r="DQ38" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR38" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS38" t="inlineStr">
@@ -20692,7 +20692,7 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28309, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/tjvtghMK/", "exitScreenshotUrl": "https://www.tradingview.com/x/E05lSpSS/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28309, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/tjvtghMK/", "exitScreenshotUrl": "https://www.tradingview.com/x/E05lSpSS/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2420.21, "sourceLowPrice": 2416.768}</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
@@ -20741,13 +20741,13 @@
         </is>
       </c>
       <c r="BJ39" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK39" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL39" t="n">
-        <v>1782553984125</v>
+        <v>1782575585792</v>
       </c>
       <c r="BM39" t="n">
         <v>2415.056</v>
@@ -20949,12 +20949,12 @@
       </c>
       <c r="DQ39" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR39" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS39" t="inlineStr">
@@ -21216,7 +21216,7 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28361, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/s41YegAx/", "exitScreenshotUrl": "https://www.tradingview.com/x/M7aa6gXW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28361, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/s41YegAx/", "exitScreenshotUrl": "https://www.tradingview.com/x/M7aa6gXW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2425.58, "sourceLowPrice": 2419.915}</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
@@ -21265,13 +21265,13 @@
         </is>
       </c>
       <c r="BJ40" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK40" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL40" t="n">
-        <v>1782553984125</v>
+        <v>1782575585792</v>
       </c>
       <c r="BM40" t="n">
         <v>2427.893</v>
@@ -21473,12 +21473,12 @@
       </c>
       <c r="DQ40" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR40" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS40" t="inlineStr">
@@ -21740,7 +21740,7 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 25084, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/PXdQt6m7/", "exitScreenshotUrl": "https://www.tradingview.com/x/A1Pf3UEQ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 25084, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/PXdQt6m7/", "exitScreenshotUrl": "https://www.tradingview.com/x/A1Pf3UEQ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2423.637, "sourceLowPrice": 2418.036}</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
@@ -21789,13 +21789,13 @@
         </is>
       </c>
       <c r="BJ41" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK41" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL41" t="n">
-        <v>1782553984125</v>
+        <v>1782575585793</v>
       </c>
       <c r="BM41" t="n">
         <v>2423.637</v>
@@ -21997,12 +21997,12 @@
       </c>
       <c r="DQ41" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR41" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS41" t="inlineStr">
@@ -22264,7 +22264,7 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28398, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/rspfdAcC/", "exitScreenshotUrl": "https://www.tradingview.com/x/mt4z58Yz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28398, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/rspfdAcC/", "exitScreenshotUrl": "https://www.tradingview.com/x/mt4z58Yz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2416.08, "sourceLowPrice": 2411.894}</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
@@ -22313,13 +22313,13 @@
         </is>
       </c>
       <c r="BJ42" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK42" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL42" t="n">
-        <v>1782553984125</v>
+        <v>1782575585793</v>
       </c>
       <c r="BM42" t="n">
         <v>2417.541</v>
@@ -22521,12 +22521,12 @@
       </c>
       <c r="DQ42" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR42" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS42" t="inlineStr">
@@ -22788,7 +22788,7 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28380, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/jPmwJyKa/", "exitScreenshotUrl": "https://www.tradingview.com/x/MVt3O4L0/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28380, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/jPmwJyKa/", "exitScreenshotUrl": "https://www.tradingview.com/x/MVt3O4L0/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2415.65, "sourceLowPrice": 2410.2}</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
@@ -22837,13 +22837,13 @@
         </is>
       </c>
       <c r="BJ43" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK43" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL43" t="n">
-        <v>1782553984125</v>
+        <v>1782575585793</v>
       </c>
       <c r="BM43" t="n">
         <v>2413.739</v>
@@ -23045,12 +23045,12 @@
       </c>
       <c r="DQ43" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR43" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS43" t="inlineStr">
@@ -23312,7 +23312,7 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28400, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/assbqjVd/", "exitScreenshotUrl": "https://www.tradingview.com/x/orBIDQgd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28400, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/assbqjVd/", "exitScreenshotUrl": "https://www.tradingview.com/x/orBIDQgd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2408.7, "sourceLowPrice": 2401.015}</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
@@ -23361,13 +23361,13 @@
         </is>
       </c>
       <c r="BJ44" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK44" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL44" t="n">
-        <v>1782553984126</v>
+        <v>1782575585794</v>
       </c>
       <c r="BM44" t="n">
         <v>2411.821</v>
@@ -23569,12 +23569,12 @@
       </c>
       <c r="DQ44" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR44" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS44" t="inlineStr">
@@ -23836,7 +23836,7 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28383, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/TlBtlHQl/", "exitScreenshotUrl": "https://www.tradingview.com/x/He2fJFzE/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28383, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/TlBtlHQl/", "exitScreenshotUrl": "https://www.tradingview.com/x/He2fJFzE/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2353.33, "sourceLowPrice": 2342.108}</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
@@ -23885,13 +23885,13 @@
         </is>
       </c>
       <c r="BJ45" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK45" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL45" t="n">
-        <v>1782553984126</v>
+        <v>1782575585794</v>
       </c>
       <c r="BM45" t="n">
         <v>2356.465</v>
@@ -24093,12 +24093,12 @@
       </c>
       <c r="DQ45" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR45" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS45" t="inlineStr">
@@ -24360,7 +24360,7 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28451, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/fmFH7lgc/", "exitScreenshotUrl": "https://www.tradingview.com/x/4wnJCJcj/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28451, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/fmFH7lgc/", "exitScreenshotUrl": "https://www.tradingview.com/x/4wnJCJcj/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2348.07, "sourceLowPrice": 2341.415}</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
@@ -24409,13 +24409,13 @@
         </is>
       </c>
       <c r="BJ46" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK46" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL46" t="n">
-        <v>1782553984126</v>
+        <v>1782575585794</v>
       </c>
       <c r="BM46" t="n">
         <v>2347.28</v>
@@ -24617,12 +24617,12 @@
       </c>
       <c r="DQ46" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR46" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS46" t="inlineStr">
@@ -24884,7 +24884,7 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28401, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/fXhUosPt/", "exitScreenshotUrl": "https://www.tradingview.com/x/5Ce2fpJY/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28401, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/fXhUosPt/", "exitScreenshotUrl": "https://www.tradingview.com/x/5Ce2fpJY/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2347.68, "sourceLowPrice": 2339.9}</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
@@ -24933,13 +24933,13 @@
         </is>
       </c>
       <c r="BJ47" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK47" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL47" t="n">
-        <v>1782553984126</v>
+        <v>1782575585795</v>
       </c>
       <c r="BM47" t="n">
         <v>2344.78</v>
@@ -25141,12 +25141,12 @@
       </c>
       <c r="DQ47" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR47" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS47" t="inlineStr">
@@ -25408,7 +25408,7 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28452, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/krBAFB1m/", "exitScreenshotUrl": "https://www.tradingview.com/x/RJA1llHF/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28452, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/krBAFB1m/", "exitScreenshotUrl": "https://www.tradingview.com/x/RJA1llHF/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2345.82, "sourceLowPrice": 2342.6}</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
@@ -25457,13 +25457,13 @@
         </is>
       </c>
       <c r="BJ48" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK48" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL48" t="n">
-        <v>1782553984126</v>
+        <v>1782575585795</v>
       </c>
       <c r="BM48" t="n">
         <v>2348.029</v>
@@ -25665,12 +25665,12 @@
       </c>
       <c r="DQ48" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR48" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS48" t="inlineStr">
@@ -25932,7 +25932,7 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28439, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/mTQ5fzDU/", "exitScreenshotUrl": "https://www.tradingview.com/x/BwzMNgdI/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28439, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/mTQ5fzDU/", "exitScreenshotUrl": "https://www.tradingview.com/x/BwzMNgdI/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2343.16, "sourceLowPrice": 2337.521}</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
@@ -25981,13 +25981,13 @@
         </is>
       </c>
       <c r="BJ49" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK49" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL49" t="n">
-        <v>1782553984126</v>
+        <v>1782575585795</v>
       </c>
       <c r="BM49" t="n">
         <v>2343.969</v>
@@ -26189,12 +26189,12 @@
       </c>
       <c r="DQ49" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR49" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS49" t="inlineStr">
@@ -26456,7 +26456,7 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28472, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/uPHTs20o/", "exitScreenshotUrl": "https://www.tradingview.com/x/g1bYHu8m/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28472, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/uPHTs20o/", "exitScreenshotUrl": "https://www.tradingview.com/x/g1bYHu8m/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2343.26, "sourceLowPrice": 2339.0}</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
@@ -26505,13 +26505,13 @@
         </is>
       </c>
       <c r="BJ50" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK50" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL50" t="n">
-        <v>1782553984127</v>
+        <v>1782575585796</v>
       </c>
       <c r="BM50" t="n">
         <v>2337.841</v>
@@ -26713,12 +26713,12 @@
       </c>
       <c r="DQ50" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR50" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS50" t="inlineStr">
@@ -26980,7 +26980,7 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28407, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/R1kZi7FP/", "exitScreenshotUrl": "https://www.tradingview.com/x/nA7AQSSf/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28407, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/R1kZi7FP/", "exitScreenshotUrl": "https://www.tradingview.com/x/nA7AQSSf/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2358.55, "sourceLowPrice": 2353.8}</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
@@ -27029,13 +27029,13 @@
         </is>
       </c>
       <c r="BJ51" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK51" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL51" t="n">
-        <v>1782553984127</v>
+        <v>1782575585796</v>
       </c>
       <c r="BM51" t="n">
         <v>2354.618</v>
@@ -27237,12 +27237,12 @@
       </c>
       <c r="DQ51" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR51" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS51" t="inlineStr">
@@ -27504,7 +27504,7 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28413, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/muxsvy8d/", "exitScreenshotUrl": "https://www.tradingview.com/x/zTnMQWmo/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28413, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/muxsvy8d/", "exitScreenshotUrl": "https://www.tradingview.com/x/zTnMQWmo/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2342.45, "sourceLowPrice": 2339.9}</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
@@ -27553,13 +27553,13 @@
         </is>
       </c>
       <c r="BJ52" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK52" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL52" t="n">
-        <v>1782553984127</v>
+        <v>1782575585797</v>
       </c>
       <c r="BM52" t="n">
         <v>2344.241</v>
@@ -27761,12 +27761,12 @@
       </c>
       <c r="DQ52" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR52" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS52" t="inlineStr">
@@ -28028,7 +28028,7 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28414, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MrQRHkXV/", "exitScreenshotUrl": "https://www.tradingview.com/x/Tmt2tr70/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28414, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MrQRHkXV/", "exitScreenshotUrl": "https://www.tradingview.com/x/Tmt2tr70/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2362.22, "sourceLowPrice": 2356.975}</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
@@ -28077,13 +28077,13 @@
         </is>
       </c>
       <c r="BJ53" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK53" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL53" t="n">
-        <v>1782553984127</v>
+        <v>1782575585797</v>
       </c>
       <c r="BM53" t="n">
         <v>2357.151</v>
@@ -28285,12 +28285,12 @@
       </c>
       <c r="DQ53" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR53" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS53" t="inlineStr">
@@ -28552,7 +28552,7 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28489, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MWh0WoFm/", "exitScreenshotUrl": "https://www.tradingview.com/x/FJQ4skxz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28489, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MWh0WoFm/", "exitScreenshotUrl": "https://www.tradingview.com/x/FJQ4skxz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2351.74, "sourceLowPrice": 2346.4}</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
@@ -28601,13 +28601,13 @@
         </is>
       </c>
       <c r="BJ54" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK54" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL54" t="n">
-        <v>1782553984127</v>
+        <v>1782575585798</v>
       </c>
       <c r="BM54" t="n">
         <v>2352.036</v>
@@ -28809,12 +28809,12 @@
       </c>
       <c r="DQ54" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR54" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS54" t="inlineStr">
@@ -29076,7 +29076,7 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28415, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/NKfR7qqN/", "exitScreenshotUrl": "https://www.tradingview.com/x/bIs06qwO/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28415, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/NKfR7qqN/", "exitScreenshotUrl": "https://www.tradingview.com/x/bIs06qwO/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2348.41, "sourceLowPrice": 2343.3}</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
@@ -29125,13 +29125,13 @@
         </is>
       </c>
       <c r="BJ55" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK55" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL55" t="n">
-        <v>1782553984127</v>
+        <v>1782575585798</v>
       </c>
       <c r="BM55" t="n">
         <v>2348.595</v>
@@ -29333,12 +29333,12 @@
       </c>
       <c r="DQ55" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR55" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS55" t="inlineStr">
@@ -29600,7 +29600,7 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28442, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MbmVODUl/", "exitScreenshotUrl": "https://www.tradingview.com/x/sumfM4mg/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28442, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MbmVODUl/", "exitScreenshotUrl": "https://www.tradingview.com/x/sumfM4mg/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2341.574, "sourceLowPrice": 2337.965}</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
@@ -29649,13 +29649,13 @@
         </is>
       </c>
       <c r="BJ56" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK56" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL56" t="n">
-        <v>1782553984127</v>
+        <v>1782575585799</v>
       </c>
       <c r="BM56" t="n">
         <v>2341.574</v>
@@ -29857,12 +29857,12 @@
       </c>
       <c r="DQ56" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR56" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS56" t="inlineStr">
@@ -30124,7 +30124,7 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28476, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/aFbl3DZW/", "exitScreenshotUrl": "https://www.tradingview.com/x/4NLZ4ALZ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28476, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/aFbl3DZW/", "exitScreenshotUrl": "https://www.tradingview.com/x/4NLZ4ALZ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2338.683, "sourceLowPrice": 2336.403}</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
@@ -30173,13 +30173,13 @@
         </is>
       </c>
       <c r="BJ57" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK57" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL57" t="n">
-        <v>1782553984128</v>
+        <v>1782575585799</v>
       </c>
       <c r="BM57" t="n">
         <v>2338.683</v>
@@ -30381,12 +30381,12 @@
       </c>
       <c r="DQ57" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR57" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS57" t="inlineStr">
@@ -30648,7 +30648,7 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28601, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/jWyxiTLq/", "exitScreenshotUrl": "https://www.tradingview.com/x/KMexMt0G/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28601, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/jWyxiTLq/", "exitScreenshotUrl": "https://www.tradingview.com/x/KMexMt0G/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2335.11, "sourceLowPrice": 2331.6}</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
@@ -30697,13 +30697,13 @@
         </is>
       </c>
       <c r="BJ58" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK58" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL58" t="n">
-        <v>1782553984128</v>
+        <v>1782575585800</v>
       </c>
       <c r="BM58" t="n">
         <v>2334.782</v>
@@ -30905,12 +30905,12 @@
       </c>
       <c r="DQ58" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR58" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS58" t="inlineStr">
@@ -31172,7 +31172,7 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28579, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AlB5cCxm/", "exitScreenshotUrl": "https://www.tradingview.com/x/cQow1s0x/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28579, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AlB5cCxm/", "exitScreenshotUrl": "https://www.tradingview.com/x/cQow1s0x/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2351.82, "sourceLowPrice": 2346.6}</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
@@ -31221,13 +31221,13 @@
         </is>
       </c>
       <c r="BJ59" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK59" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL59" t="n">
-        <v>1782553984128</v>
+        <v>1782575585800</v>
       </c>
       <c r="BM59" t="n">
         <v>2344.647</v>
@@ -31429,12 +31429,12 @@
       </c>
       <c r="DQ59" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR59" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS59" t="inlineStr">
@@ -31696,7 +31696,7 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28604, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ZhIV3QS1/", "exitScreenshotUrl": "https://www.tradingview.com/x/mPGQ8Iz9/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28604, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ZhIV3QS1/", "exitScreenshotUrl": "https://www.tradingview.com/x/mPGQ8Iz9/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2338.22, "sourceLowPrice": 2329.3}</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
@@ -31745,13 +31745,13 @@
         </is>
       </c>
       <c r="BJ60" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK60" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL60" t="n">
-        <v>1782553984128</v>
+        <v>1782575585801</v>
       </c>
       <c r="BM60" t="n">
         <v>2341.421</v>
@@ -31953,12 +31953,12 @@
       </c>
       <c r="DQ60" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR60" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS60" t="inlineStr">
@@ -32220,7 +32220,7 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28658, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9cR212Zy/", "exitScreenshotUrl": "https://www.tradingview.com/x/gceUW4oY/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28658, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9cR212Zy/", "exitScreenshotUrl": "https://www.tradingview.com/x/gceUW4oY/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2334.67, "sourceLowPrice": 2327.635}</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
@@ -32269,13 +32269,13 @@
         </is>
       </c>
       <c r="BJ61" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK61" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL61" t="n">
-        <v>1782553984128</v>
+        <v>1782575585801</v>
       </c>
       <c r="BM61" t="n">
         <v>2336.327</v>
@@ -32477,12 +32477,12 @@
       </c>
       <c r="DQ61" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR61" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS61" t="inlineStr">
@@ -32744,7 +32744,7 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28605, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/OF3gWNl2/", "exitScreenshotUrl": "https://www.tradingview.com/x/ddRCBEa4/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28605, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/OF3gWNl2/", "exitScreenshotUrl": "https://www.tradingview.com/x/ddRCBEa4/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2336.69, "sourceLowPrice": 2331.8}</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
@@ -32793,13 +32793,13 @@
         </is>
       </c>
       <c r="BJ62" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK62" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL62" t="n">
-        <v>1782553984128</v>
+        <v>1782575585802</v>
       </c>
       <c r="BM62" t="n">
         <v>2333.797</v>
@@ -33001,12 +33001,12 @@
       </c>
       <c r="DQ62" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR62" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS62" t="inlineStr">
@@ -33268,7 +33268,7 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28595, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/DyvsWt23/", "exitScreenshotUrl": "https://www.tradingview.com/x/u3ZVecEf/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28595, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/DyvsWt23/", "exitScreenshotUrl": "https://www.tradingview.com/x/u3ZVecEf/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2328.53, "sourceLowPrice": 2324.1}</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
@@ -33317,13 +33317,13 @@
         </is>
       </c>
       <c r="BJ63" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK63" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL63" t="n">
-        <v>1782553984129</v>
+        <v>1782575585802</v>
       </c>
       <c r="BM63" t="n">
         <v>2324.387</v>
@@ -33525,12 +33525,12 @@
       </c>
       <c r="DQ63" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR63" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS63" t="inlineStr">
@@ -33792,7 +33792,7 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28620, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/0tRURqTb/", "exitScreenshotUrl": "https://www.tradingview.com/x/x886IDNy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28620, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/0tRURqTb/", "exitScreenshotUrl": "https://www.tradingview.com/x/x886IDNy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2345.24, "sourceLowPrice": 2335.1}</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
@@ -33841,13 +33841,13 @@
         </is>
       </c>
       <c r="BJ64" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK64" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL64" t="n">
-        <v>1782553984129</v>
+        <v>1782575585803</v>
       </c>
       <c r="BM64" t="n">
         <v>2337.982</v>
@@ -34049,12 +34049,12 @@
       </c>
       <c r="DQ64" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR64" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS64" t="inlineStr">
@@ -34316,7 +34316,7 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28661, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/3D37aPmg/", "exitScreenshotUrl": "https://www.tradingview.com/x/S64dm61o/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28661, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/3D37aPmg/", "exitScreenshotUrl": "https://www.tradingview.com/x/S64dm61o/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2349.0, "sourceLowPrice": 2345.0}</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
@@ -34365,13 +34365,13 @@
         </is>
       </c>
       <c r="BJ65" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK65" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL65" t="n">
-        <v>1782553984129</v>
+        <v>1782575585803</v>
       </c>
       <c r="BM65" t="n">
         <v>2343.37</v>
@@ -34573,12 +34573,12 @@
       </c>
       <c r="DQ65" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR65" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS65" t="inlineStr">
@@ -34840,7 +34840,7 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28641, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/w46rEdJQ/", "exitScreenshotUrl": "https://www.tradingview.com/x/hqVNU3N3/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28641, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/w46rEdJQ/", "exitScreenshotUrl": "https://www.tradingview.com/x/hqVNU3N3/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2336.0, "sourceLowPrice": 2330.7}</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
@@ -34889,13 +34889,13 @@
         </is>
       </c>
       <c r="BJ66" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK66" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL66" t="n">
-        <v>1782553984129</v>
+        <v>1782575585805</v>
       </c>
       <c r="BM66" t="n">
         <v>2336.995</v>
@@ -35097,12 +35097,12 @@
       </c>
       <c r="DQ66" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR66" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS66" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28662, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MHUOR8gb/", "exitScreenshotUrl": "https://www.tradingview.com/x/bLPpS3XK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28662, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MHUOR8gb/", "exitScreenshotUrl": "https://www.tradingview.com/x/bLPpS3XK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2321.949, "sourceLowPrice": 2315.704}</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
@@ -35413,13 +35413,13 @@
         </is>
       </c>
       <c r="BJ67" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK67" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL67" t="n">
-        <v>1782553984129</v>
+        <v>1782575585805</v>
       </c>
       <c r="BM67" t="n">
         <v>2326.819</v>
@@ -35621,12 +35621,12 @@
       </c>
       <c r="DQ67" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR67" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS67" t="inlineStr">
@@ -35888,7 +35888,7 @@
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28642, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/bqoChwTO/", "exitScreenshotUrl": "https://www.tradingview.com/x/98gZi68e/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28642, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/bqoChwTO/", "exitScreenshotUrl": "https://www.tradingview.com/x/98gZi68e/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2329.65, "sourceLowPrice": 2324.6}</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
@@ -35937,13 +35937,13 @@
         </is>
       </c>
       <c r="BJ68" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK68" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL68" t="n">
-        <v>1782553984130</v>
+        <v>1782575585805</v>
       </c>
       <c r="BM68" t="n">
         <v>2326.026</v>
@@ -36145,12 +36145,12 @@
       </c>
       <c r="DQ68" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR68" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS68" t="inlineStr">
@@ -36412,7 +36412,7 @@
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28606, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AU51CmFt/", "exitScreenshotUrl": "https://www.tradingview.com/x/H9JG4CXS/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28606, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AU51CmFt/", "exitScreenshotUrl": "https://www.tradingview.com/x/H9JG4CXS/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2335.11, "sourceLowPrice": 2331.5}</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
@@ -36461,13 +36461,13 @@
         </is>
       </c>
       <c r="BJ69" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK69" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL69" t="n">
-        <v>1782553984130</v>
+        <v>1782575585806</v>
       </c>
       <c r="BM69" t="n">
         <v>2331.701</v>
@@ -36669,12 +36669,12 @@
       </c>
       <c r="DQ69" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR69" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS69" t="inlineStr">
@@ -36936,7 +36936,7 @@
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28622, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/UXEwWABV/", "exitScreenshotUrl": "https://www.tradingview.com/x/hMS4FOY1/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28622, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/UXEwWABV/", "exitScreenshotUrl": "https://www.tradingview.com/x/hMS4FOY1/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2352.711, "sourceLowPrice": 2343.7}</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
@@ -36985,13 +36985,13 @@
         </is>
       </c>
       <c r="BJ70" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK70" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL70" t="n">
-        <v>1782553984130</v>
+        <v>1782575585806</v>
       </c>
       <c r="BM70" t="n">
         <v>2340.627</v>
@@ -37193,12 +37193,12 @@
       </c>
       <c r="DQ70" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR70" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS70" t="inlineStr">
@@ -37460,7 +37460,7 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28623, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/IvQxoxe5/", "exitScreenshotUrl": "https://www.tradingview.com/x/X2FD5z5o/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28623, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/IvQxoxe5/", "exitScreenshotUrl": "https://www.tradingview.com/x/X2FD5z5o/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2354.09, "sourceLowPrice": 2349.51}</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
@@ -37509,13 +37509,13 @@
         </is>
       </c>
       <c r="BJ71" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK71" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL71" t="n">
-        <v>1782553984130</v>
+        <v>1782575585807</v>
       </c>
       <c r="BM71" t="n">
         <v>2347.068</v>
@@ -37717,12 +37717,12 @@
       </c>
       <c r="DQ71" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR71" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS71" t="inlineStr">
@@ -37984,7 +37984,7 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28607, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9W1fTQuq/", "exitScreenshotUrl": "https://www.tradingview.com/x/ViSl8TNr/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28607, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9W1fTQuq/", "exitScreenshotUrl": "https://www.tradingview.com/x/ViSl8TNr/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2357.34, "sourceLowPrice": 2353.6}</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
@@ -38033,13 +38033,13 @@
         </is>
       </c>
       <c r="BJ72" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK72" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL72" t="n">
-        <v>1782553984130</v>
+        <v>1782575585807</v>
       </c>
       <c r="BM72" t="n">
         <v>2351.395</v>
@@ -38241,12 +38241,12 @@
       </c>
       <c r="DQ72" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR72" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS72" t="inlineStr">
@@ -38508,7 +38508,7 @@
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28609, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AZAPIngv/", "exitScreenshotUrl": "https://www.tradingview.com/x/n7hVFF23/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28609, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AZAPIngv/", "exitScreenshotUrl": "https://www.tradingview.com/x/n7hVFF23/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2363.03, "sourceLowPrice": 2359.6}</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
@@ -38557,13 +38557,13 @@
         </is>
       </c>
       <c r="BJ73" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK73" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL73" t="n">
-        <v>1782553984130</v>
+        <v>1782575585807</v>
       </c>
       <c r="BM73" t="n">
         <v>2363.688</v>
@@ -38765,12 +38765,12 @@
       </c>
       <c r="DQ73" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR73" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS73" t="inlineStr">
@@ -39032,7 +39032,7 @@
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28665, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/4FhomDYt/", "exitScreenshotUrl": "https://www.tradingview.com/x/Z2hSwYHj/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28665, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/4FhomDYt/", "exitScreenshotUrl": "https://www.tradingview.com/x/Z2hSwYHj/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2363.19, "sourceLowPrice": 2360.5}</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
@@ -39081,13 +39081,13 @@
         </is>
       </c>
       <c r="BJ74" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK74" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL74" t="n">
-        <v>1782553984130</v>
+        <v>1782575585808</v>
       </c>
       <c r="BM74" t="n">
         <v>2362.593</v>
@@ -39289,12 +39289,12 @@
       </c>
       <c r="DQ74" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR74" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS74" t="inlineStr">
@@ -39556,7 +39556,7 @@
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28667, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/20nVepz9/", "exitScreenshotUrl": "https://www.tradingview.com/x/FmQoAF4O/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28667, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/20nVepz9/", "exitScreenshotUrl": "https://www.tradingview.com/x/FmQoAF4O/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2371.86, "sourceLowPrice": 2366.2}</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
@@ -39605,13 +39605,13 @@
         </is>
       </c>
       <c r="BJ75" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK75" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL75" t="n">
-        <v>1782553984131</v>
+        <v>1782575585808</v>
       </c>
       <c r="BM75" t="n">
         <v>2364.129</v>
@@ -39813,12 +39813,12 @@
       </c>
       <c r="DQ75" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR75" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS75" t="inlineStr">
@@ -40080,7 +40080,7 @@
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28598, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/3hfCYyY0/", "exitScreenshotUrl": "https://www.tradingview.com/x/j54VUu1O/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28598, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/3hfCYyY0/", "exitScreenshotUrl": "https://www.tradingview.com/x/j54VUu1O/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2377.761, "sourceLowPrice": 2371.1}</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
@@ -40129,13 +40129,13 @@
         </is>
       </c>
       <c r="BJ76" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK76" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL76" t="n">
-        <v>1782553984131</v>
+        <v>1782575585808</v>
       </c>
       <c r="BM76" t="n">
         <v>2369.021</v>
@@ -40337,12 +40337,12 @@
       </c>
       <c r="DQ76" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR76" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS76" t="inlineStr">
@@ -40604,7 +40604,7 @@
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 17238, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AzKmhYPZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/aqmElclx/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 17238, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AzKmhYPZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/aqmElclx/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2351.05, "sourceLowPrice": 2342.424}</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
@@ -40653,13 +40653,13 @@
         </is>
       </c>
       <c r="BJ77" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK77" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL77" t="n">
-        <v>1782553984131</v>
+        <v>1782575585809</v>
       </c>
       <c r="BM77" t="n">
         <v>2354.824</v>
@@ -40861,12 +40861,12 @@
       </c>
       <c r="DQ77" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR77" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS77" t="inlineStr">
@@ -41128,7 +41128,7 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28644, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/oBTwB2OL/", "exitScreenshotUrl": "https://www.tradingview.com/x/w9TI27Un/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28644, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/oBTwB2OL/", "exitScreenshotUrl": "https://www.tradingview.com/x/w9TI27Un/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2315.551, "sourceLowPrice": 2306.618}</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
@@ -41177,13 +41177,13 @@
         </is>
       </c>
       <c r="BJ78" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK78" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL78" t="n">
-        <v>1782553984131</v>
+        <v>1782575585809</v>
       </c>
       <c r="BM78" t="n">
         <v>2317.824</v>
@@ -41385,12 +41385,12 @@
       </c>
       <c r="DQ78" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR78" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS78" t="inlineStr">
@@ -41652,7 +41652,7 @@
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 18551, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/gpW9dZTu/", "exitScreenshotUrl": "https://www.tradingview.com/x/Gv1UqXw0/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 18551, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/gpW9dZTu/", "exitScreenshotUrl": "https://www.tradingview.com/x/Gv1UqXw0/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2310.08, "sourceLowPrice": 2304.8}</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
@@ -41701,13 +41701,13 @@
         </is>
       </c>
       <c r="BJ79" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK79" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL79" t="n">
-        <v>1782553984131</v>
+        <v>1782575585809</v>
       </c>
       <c r="BM79" t="n">
         <v>2313.241</v>
@@ -41909,12 +41909,12 @@
       </c>
       <c r="DQ79" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR79" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS79" t="inlineStr">
@@ -42176,7 +42176,7 @@
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 21659, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qFIEHlKX/", "exitScreenshotUrl": "https://www.tradingview.com/x/Vj90lc2D/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 21659, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qFIEHlKX/", "exitScreenshotUrl": "https://www.tradingview.com/x/Vj90lc2D/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2307.14, "sourceLowPrice": 2302.948}</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
@@ -42225,13 +42225,13 @@
         </is>
       </c>
       <c r="BJ80" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK80" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL80" t="n">
-        <v>1782553984131</v>
+        <v>1782575585809</v>
       </c>
       <c r="BM80" t="n">
         <v>2309.814</v>
@@ -42433,12 +42433,12 @@
       </c>
       <c r="DQ80" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR80" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS80" t="inlineStr">
@@ -42700,7 +42700,7 @@
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 22072, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/VZY4fThQ/", "exitScreenshotUrl": "https://www.tradingview.com/x/i54J1LLH/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 22072, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/VZY4fThQ/", "exitScreenshotUrl": "https://www.tradingview.com/x/i54J1LLH/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2307.832, "sourceLowPrice": 2305.312}</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
@@ -42749,13 +42749,13 @@
         </is>
       </c>
       <c r="BJ81" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK81" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL81" t="n">
-        <v>1782553984131</v>
+        <v>1782575585810</v>
       </c>
       <c r="BM81" t="n">
         <v>2305.312</v>
@@ -42957,12 +42957,12 @@
       </c>
       <c r="DQ81" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR81" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS81" t="inlineStr">
@@ -43224,7 +43224,7 @@
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28645, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/d4ygHVMv/", "exitScreenshotUrl": "https://www.tradingview.com/x/6zAuTNCD/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28645, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/d4ygHVMv/", "exitScreenshotUrl": "https://www.tradingview.com/x/6zAuTNCD/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2313.0, "sourceLowPrice": 2307.7}</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
@@ -43273,13 +43273,13 @@
         </is>
       </c>
       <c r="BJ82" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK82" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL82" t="n">
-        <v>1782553984132</v>
+        <v>1782575585810</v>
       </c>
       <c r="BM82" t="n">
         <v>2306.069</v>
@@ -43481,12 +43481,12 @@
       </c>
       <c r="DQ82" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR82" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS82" t="inlineStr">
@@ -43748,7 +43748,7 @@
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 22216, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/nDpUf1Ab/", "exitScreenshotUrl": "https://www.tradingview.com/x/Digg8wjv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 22216, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/nDpUf1Ab/", "exitScreenshotUrl": "https://www.tradingview.com/x/Digg8wjv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2307.76, "sourceLowPrice": 2304.5}</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
@@ -43797,13 +43797,13 @@
         </is>
       </c>
       <c r="BJ83" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK83" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL83" t="n">
-        <v>1782553984132</v>
+        <v>1782575585811</v>
       </c>
       <c r="BM83" t="n">
         <v>2303.447</v>
@@ -44005,12 +44005,12 @@
       </c>
       <c r="DQ83" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR83" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS83" t="inlineStr">
@@ -44272,7 +44272,7 @@
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 22790, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/w0A8BEBv/", "exitScreenshotUrl": "https://www.tradingview.com/x/y4FnXweb/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 22790, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/w0A8BEBv/", "exitScreenshotUrl": "https://www.tradingview.com/x/y4FnXweb/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2314.38, "sourceLowPrice": 2310.5}</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
@@ -44321,13 +44321,13 @@
         </is>
       </c>
       <c r="BJ84" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK84" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL84" t="n">
-        <v>1782553984132</v>
+        <v>1782575585811</v>
       </c>
       <c r="BM84" t="n">
         <v>2313.09</v>
@@ -44529,12 +44529,12 @@
       </c>
       <c r="DQ84" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR84" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS84" t="inlineStr">
@@ -44796,7 +44796,7 @@
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28730, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/yDZImHkS/", "exitScreenshotUrl": "https://www.tradingview.com/x/2oOrAucd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28730, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/yDZImHkS/", "exitScreenshotUrl": "https://www.tradingview.com/x/2oOrAucd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2312.39, "sourceLowPrice": 2306.675}</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
@@ -44845,13 +44845,13 @@
         </is>
       </c>
       <c r="BJ85" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK85" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL85" t="n">
-        <v>1782553984132</v>
+        <v>1782575585811</v>
       </c>
       <c r="BM85" t="n">
         <v>2312.522</v>
@@ -45053,12 +45053,12 @@
       </c>
       <c r="DQ85" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR85" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS85" t="inlineStr">
@@ -45320,7 +45320,7 @@
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28692, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/mysHW1IT/", "exitScreenshotUrl": "https://www.tradingview.com/x/TwpFvksy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28692, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/mysHW1IT/", "exitScreenshotUrl": "https://www.tradingview.com/x/TwpFvksy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2315.75, "sourceLowPrice": 2312.688}</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
@@ -45369,13 +45369,13 @@
         </is>
       </c>
       <c r="BJ86" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK86" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL86" t="n">
-        <v>1782553984132</v>
+        <v>1782575585812</v>
       </c>
       <c r="BM86" t="n">
         <v>2313.406</v>
@@ -45577,12 +45577,12 @@
       </c>
       <c r="DQ86" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR86" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS86" t="inlineStr">
@@ -45844,7 +45844,7 @@
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28731, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/tP5qz7XH/", "exitScreenshotUrl": "https://www.tradingview.com/x/TL4BxDiC/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28731, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/tP5qz7XH/", "exitScreenshotUrl": "https://www.tradingview.com/x/TL4BxDiC/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2337.18, "sourceLowPrice": 2329.5}</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
@@ -45893,13 +45893,13 @@
         </is>
       </c>
       <c r="BJ87" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK87" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL87" t="n">
-        <v>1782553984132</v>
+        <v>1782575585812</v>
       </c>
       <c r="BM87" t="n">
         <v>2327.212</v>
@@ -46101,12 +46101,12 @@
       </c>
       <c r="DQ87" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR87" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS87" t="inlineStr">
@@ -46368,7 +46368,7 @@
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28734, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/hp3pCnfw/", "exitScreenshotUrl": "https://www.tradingview.com/x/z4RO2lfq/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28734, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/hp3pCnfw/", "exitScreenshotUrl": "https://www.tradingview.com/x/z4RO2lfq/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2315.91, "sourceLowPrice": 2308.962}</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
@@ -46417,13 +46417,13 @@
         </is>
       </c>
       <c r="BJ88" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK88" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL88" t="n">
-        <v>1782553984132</v>
+        <v>1782575585812</v>
       </c>
       <c r="BM88" t="n">
         <v>2311.398</v>
@@ -46625,12 +46625,12 @@
       </c>
       <c r="DQ88" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR88" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS88" t="inlineStr">
@@ -46892,7 +46892,7 @@
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 26781, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/hsMsS3pG/", "exitScreenshotUrl": "https://www.tradingview.com/x/uAzeiqIO/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 26781, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/hsMsS3pG/", "exitScreenshotUrl": "https://www.tradingview.com/x/uAzeiqIO/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2321.72, "sourceLowPrice": 2316.697}</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
@@ -46941,13 +46941,13 @@
         </is>
       </c>
       <c r="BJ89" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK89" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL89" t="n">
-        <v>1782553984133</v>
+        <v>1782575585813</v>
       </c>
       <c r="BM89" t="n">
         <v>2314.485</v>
@@ -47149,12 +47149,12 @@
       </c>
       <c r="DQ89" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR89" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS89" t="inlineStr">
@@ -47416,7 +47416,7 @@
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 1306, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/QCqpCXux/", "exitScreenshotUrl": "https://www.tradingview.com/x/2fJBAnIr/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 1306, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/QCqpCXux/", "exitScreenshotUrl": "https://www.tradingview.com/x/2fJBAnIr/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2322.66, "sourceLowPrice": 2319.0}</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
@@ -47465,13 +47465,13 @@
         </is>
       </c>
       <c r="BJ90" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK90" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL90" t="n">
-        <v>1782553984133</v>
+        <v>1782575585813</v>
       </c>
       <c r="BM90" t="n">
         <v>2319.546</v>
@@ -47673,12 +47673,12 @@
       </c>
       <c r="DQ90" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR90" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS90" t="inlineStr">
@@ -47940,7 +47940,7 @@
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 26057, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/opk8j7ki/", "exitScreenshotUrl": "https://www.tradingview.com/x/jUnkSGll/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 26057, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/opk8j7ki/", "exitScreenshotUrl": "https://www.tradingview.com/x/jUnkSGll/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2327.64, "sourceLowPrice": 2321.8}</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
@@ -47989,13 +47989,13 @@
         </is>
       </c>
       <c r="BJ91" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BK91" t="n">
-        <v>928988</v>
+        <v>34</v>
       </c>
       <c r="BL91" t="n">
-        <v>1782553984133</v>
+        <v>1782575585813</v>
       </c>
       <c r="BM91" t="n">
         <v>2323.108</v>
@@ -48197,12 +48197,12 @@
       </c>
       <c r="DQ91" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DR91" t="inlineStr">
         <is>
-          <t>journalAccount:928988</t>
+          <t>journalAccount:56</t>
         </is>
       </c>
       <c r="DS91" t="inlineStr">

--- a/mentor data/hadier 5-talaria-adapted.xlsx
+++ b/mentor data/hadier 5-talaria-adapted.xlsx
@@ -1304,7 +1304,7 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28255, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/jRxeSy9V/", "exitScreenshotUrl": "https://www.tradingview.com/x/jRxeSy9V/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2301.86, "sourceLowPrice": 2294.9}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28255, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/jRxeSy9V/", "exitScreenshotUrl": "https://www.tradingview.com/x/jRxeSy9V/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2301.86, "sourceLowPrice": 2294.9, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1359,7 +1359,7 @@
         <v>34</v>
       </c>
       <c r="BL2" t="n">
-        <v>1782575585776</v>
+        <v>1782578992375</v>
       </c>
       <c r="BM2" t="n">
         <v>2289.809</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28199, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/PIEyLfQh/", "exitScreenshotUrl": "https://www.tradingview.com/x/W0rZm9XJ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2316.46, "sourceLowPrice": 2313.7}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28199, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/PIEyLfQh/", "exitScreenshotUrl": "https://www.tradingview.com/x/W0rZm9XJ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2316.46, "sourceLowPrice": 2313.7, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1883,7 +1883,7 @@
         <v>34</v>
       </c>
       <c r="BL3" t="n">
-        <v>1782575585777</v>
+        <v>1782578992375</v>
       </c>
       <c r="BM3" t="n">
         <v>2318.202</v>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28182, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/UAMJBO4F/", "exitScreenshotUrl": "https://www.tradingview.com/x/pVNahenz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2315.18, "sourceLowPrice": 2310.5}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28182, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/UAMJBO4F/", "exitScreenshotUrl": "https://www.tradingview.com/x/pVNahenz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2315.18, "sourceLowPrice": 2310.5, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -2407,7 +2407,7 @@
         <v>34</v>
       </c>
       <c r="BL4" t="n">
-        <v>1782575585777</v>
+        <v>1782578992375</v>
       </c>
       <c r="BM4" t="n">
         <v>2316.26</v>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="DO4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 2316.26, "new": 2316.982, "at": 1714451400000}]</t>
         </is>
       </c>
       <c r="DP4" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28234, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/b0romhzm/", "exitScreenshotUrl": "https://www.tradingview.com/x/3hIitC5V/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2302.51, "sourceLowPrice": 2293.018}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28234, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/b0romhzm/", "exitScreenshotUrl": "https://www.tradingview.com/x/3hIitC5V/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2302.51, "sourceLowPrice": 2293.018, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -2931,7 +2931,7 @@
         <v>34</v>
       </c>
       <c r="BL5" t="n">
-        <v>1782575585778</v>
+        <v>1782578992375</v>
       </c>
       <c r="BM5" t="n">
         <v>2302.938</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 18585, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/WfIEhctn/", "exitScreenshotUrl": "https://www.tradingview.com/x/csXLFkS4/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2300.52, "sourceLowPrice": 2293.018}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 18585, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/WfIEhctn/", "exitScreenshotUrl": "https://www.tradingview.com/x/csXLFkS4/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2300.52, "sourceLowPrice": 2293.018, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -3455,7 +3455,7 @@
         <v>34</v>
       </c>
       <c r="BL6" t="n">
-        <v>1782575585778</v>
+        <v>1782578992375</v>
       </c>
       <c r="BM6" t="n">
         <v>2299.357</v>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28253, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qfF2m4SA/", "exitScreenshotUrl": "https://www.tradingview.com/x/atW9ItK5/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2309.287, "sourceLowPrice": 2302.385}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28253, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qfF2m4SA/", "exitScreenshotUrl": "https://www.tradingview.com/x/atW9ItK5/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2309.287, "sourceLowPrice": 2302.385, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -3979,7 +3979,7 @@
         <v>34</v>
       </c>
       <c r="BL7" t="n">
-        <v>1782575585779</v>
+        <v>1782578992376</v>
       </c>
       <c r="BM7" t="n">
         <v>2300.332</v>
@@ -4160,11 +4160,11 @@
       </c>
       <c r="DL7" t="inlineStr">
         <is>
-          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN7" t="inlineStr">
         <is>
@@ -4238,12 +4238,12 @@
       </c>
       <c r="EF7" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "fomo", "label": "FOMO", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 1000, "evidence": "Entered after the move was already extended without a fresh setup.", "detected_at": "2024-05-01T11:27:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH7" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 18921, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ukXfHVE6/", "exitScreenshotUrl": "https://www.tradingview.com/x/LkazmjPv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2310.46, "sourceLowPrice": 2304.3}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 18921, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ukXfHVE6/", "exitScreenshotUrl": "https://www.tradingview.com/x/LkazmjPv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2310.46, "sourceLowPrice": 2304.3, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -4503,7 +4503,7 @@
         <v>34</v>
       </c>
       <c r="BL8" t="n">
-        <v>1782575585779</v>
+        <v>1782578992376</v>
       </c>
       <c r="BM8" t="n">
         <v>2304.719</v>
@@ -4684,11 +4684,11 @@
       </c>
       <c r="DL8" t="inlineStr">
         <is>
-          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN8" t="inlineStr">
         <is>
@@ -4762,12 +4762,12 @@
       </c>
       <c r="EF8" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "size_up", "label": "Size Up", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 1000, "evidence": "Position size exceeded the planned risk envelope.", "detected_at": "2024-05-01T12:03:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH8" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 20122, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Hus5JQfv/", "exitScreenshotUrl": "https://www.tradingview.com/x/qOkEoVR0/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2306.98, "sourceLowPrice": 2302.0}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 20122, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/Hus5JQfv/", "exitScreenshotUrl": "https://www.tradingview.com/x/qOkEoVR0/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2306.98, "sourceLowPrice": 2302.0, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -5027,7 +5027,7 @@
         <v>34</v>
       </c>
       <c r="BL9" t="n">
-        <v>1782575585779</v>
+        <v>1782578992376</v>
       </c>
       <c r="BM9" t="n">
         <v>2302.805</v>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28202, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AtJcWBS2/", "exitScreenshotUrl": "https://www.tradingview.com/x/8uZWmH5T/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2311.1, "sourceLowPrice": 2306.5}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28202, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AtJcWBS2/", "exitScreenshotUrl": "https://www.tradingview.com/x/8uZWmH5T/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2311.1, "sourceLowPrice": 2306.5, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -5551,7 +5551,7 @@
         <v>34</v>
       </c>
       <c r="BL10" t="n">
-        <v>1782575585780</v>
+        <v>1782578992376</v>
       </c>
       <c r="BM10" t="n">
         <v>2312.001</v>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 20169, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/YYiJB7mR/", "exitScreenshotUrl": "https://www.tradingview.com/x/mU7a5ueZ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2308.14, "sourceLowPrice": 2304.1}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 20169, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/YYiJB7mR/", "exitScreenshotUrl": "https://www.tradingview.com/x/mU7a5ueZ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2308.14, "sourceLowPrice": 2304.1, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -6075,7 +6075,7 @@
         <v>34</v>
       </c>
       <c r="BL11" t="n">
-        <v>1782575585780</v>
+        <v>1782578992376</v>
       </c>
       <c r="BM11" t="n">
         <v>2309.928</v>
@@ -6256,11 +6256,11 @@
       </c>
       <c r="DL11" t="inlineStr">
         <is>
-          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN11" t="inlineStr">
         <is>
@@ -6334,12 +6334,12 @@
       </c>
       <c r="EF11" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "early_exit", "label": "Early Exit", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 1000, "evidence": "Closed before the planned target without a rule-based trigger.", "detected_at": "2024-05-02T04:28:00.000Z"}, {"type": "overtrade", "label": "Overtrading", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 1000, "evidence": "Took an extra trade outside the planned session window.", "detected_at": "2024-05-02T04:28:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH11" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28254, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/c3LwRxSZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/0PbXEiKd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2307.24, "sourceLowPrice": 2302.914}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28254, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/c3LwRxSZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/0PbXEiKd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2307.24, "sourceLowPrice": 2302.914, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -6599,7 +6599,7 @@
         <v>34</v>
       </c>
       <c r="BL12" t="n">
-        <v>1782575585781</v>
+        <v>1782578992377</v>
       </c>
       <c r="BM12" t="n">
         <v>2308.041</v>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28204, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/8iNqHntm/", "exitScreenshotUrl": "https://www.tradingview.com/x/V7JCHdts/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2302.34, "sourceLowPrice": 2297.6}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28204, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/8iNqHntm/", "exitScreenshotUrl": "https://www.tradingview.com/x/V7JCHdts/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2302.34, "sourceLowPrice": 2297.6, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -7123,7 +7123,7 @@
         <v>34</v>
       </c>
       <c r="BL13" t="n">
-        <v>1782575585781</v>
+        <v>1782578992377</v>
       </c>
       <c r="BM13" t="n">
         <v>2297.26</v>
@@ -7592,7 +7592,7 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28267, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/lXVzZDyF/", "exitScreenshotUrl": "https://www.tradingview.com/x/pu5BtGwk/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2323.69, "sourceLowPrice": 2319.395}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28267, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/lXVzZDyF/", "exitScreenshotUrl": "https://www.tradingview.com/x/pu5BtGwk/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2323.69, "sourceLowPrice": 2319.395, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -7647,7 +7647,7 @@
         <v>34</v>
       </c>
       <c r="BL14" t="n">
-        <v>1782575585781</v>
+        <v>1782578992377</v>
       </c>
       <c r="BM14" t="n">
         <v>2322.981</v>
@@ -8116,7 +8116,7 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28256, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/TfuaYUaO/", "exitScreenshotUrl": "https://www.tradingview.com/x/IOF3W1Qc/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2326.191, "sourceLowPrice": 2318.535}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28256, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/TfuaYUaO/", "exitScreenshotUrl": "https://www.tradingview.com/x/IOF3W1Qc/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2326.191, "sourceLowPrice": 2318.535, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -8171,7 +8171,7 @@
         <v>34</v>
       </c>
       <c r="BL15" t="n">
-        <v>1782575585782</v>
+        <v>1782578992377</v>
       </c>
       <c r="BM15" t="n">
         <v>2325.153</v>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28268, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/mClIVHU6/", "exitScreenshotUrl": "https://www.tradingview.com/x/rDz3tNzq/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2319.16, "sourceLowPrice": 2312.7}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28268, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/mClIVHU6/", "exitScreenshotUrl": "https://www.tradingview.com/x/rDz3tNzq/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2319.16, "sourceLowPrice": 2312.7, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -8695,7 +8695,7 @@
         <v>34</v>
       </c>
       <c r="BL16" t="n">
-        <v>1782575585782</v>
+        <v>1782578992377</v>
       </c>
       <c r="BM16" t="n">
         <v>2320.167</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="DO16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 2320.167, "new": 2320.821, "at": 1715079780000}]</t>
         </is>
       </c>
       <c r="DP16" t="n">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28206, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/TTKcNwhr/", "exitScreenshotUrl": "https://www.tradingview.com/x/TpJoXp6K/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2316.112, "sourceLowPrice": 2312.4}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28206, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/TTKcNwhr/", "exitScreenshotUrl": "https://www.tradingview.com/x/TpJoXp6K/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2316.112, "sourceLowPrice": 2312.4, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -9219,7 +9219,7 @@
         <v>34</v>
       </c>
       <c r="BL17" t="n">
-        <v>1782575585783</v>
+        <v>1782578992377</v>
       </c>
       <c r="BM17" t="n">
         <v>2316.112</v>
@@ -9688,7 +9688,7 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 20790, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9AzlOCXX/", "exitScreenshotUrl": "https://www.tradingview.com/x/fFLGT4pD/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2321.14, "sourceLowPrice": 2317.371}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 20790, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9AzlOCXX/", "exitScreenshotUrl": "https://www.tradingview.com/x/fFLGT4pD/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "missed-trade", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2321.14, "sourceLowPrice": 2317.371, "rule_outcome": "missed", "reason": "Missed trade", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -9743,7 +9743,7 @@
         <v>34</v>
       </c>
       <c r="BL18" t="n">
-        <v>1782575585783</v>
+        <v>1782578992378</v>
       </c>
       <c r="BM18" t="n">
         <v>2318.24</v>
@@ -9924,11 +9924,11 @@
       </c>
       <c r="DL18" t="inlineStr">
         <is>
-          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "missed-trade"}</t>
         </is>
       </c>
       <c r="DM18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN18" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="EF18" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>missed-trade</t>
         </is>
       </c>
       <c r="EG18" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 21967, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/vOAg15bN/", "exitScreenshotUrl": "https://www.tradingview.com/x/DTGSbQGd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2313.06, "sourceLowPrice": 2308.7}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 21967, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/vOAg15bN/", "exitScreenshotUrl": "https://www.tradingview.com/x/DTGSbQGd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2313.06, "sourceLowPrice": 2308.7, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -10267,7 +10267,7 @@
         <v>34</v>
       </c>
       <c r="BL19" t="n">
-        <v>1782575585784</v>
+        <v>1782578992378</v>
       </c>
       <c r="BM19" t="n">
         <v>2313.328</v>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28280, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/bZFIl2Qo/", "exitScreenshotUrl": "https://www.tradingview.com/x/r8u9CKtk/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2337.67, "sourceLowPrice": 2332.958}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28280, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/bZFIl2Qo/", "exitScreenshotUrl": "https://www.tradingview.com/x/r8u9CKtk/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2337.67, "sourceLowPrice": 2332.958, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
@@ -10791,7 +10791,7 @@
         <v>34</v>
       </c>
       <c r="BL20" t="n">
-        <v>1782575585784</v>
+        <v>1782578992378</v>
       </c>
       <c r="BM20" t="n">
         <v>2330.21</v>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 22894, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/PK3dh2ZJ/", "exitScreenshotUrl": "https://www.tradingview.com/x/bW4InguD/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2372.18, "sourceLowPrice": 2367.1}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 22894, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/PK3dh2ZJ/", "exitScreenshotUrl": "https://www.tradingview.com/x/bW4InguD/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2372.18, "sourceLowPrice": 2367.1, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
@@ -11315,7 +11315,7 @@
         <v>34</v>
       </c>
       <c r="BL21" t="n">
-        <v>1782575585785</v>
+        <v>1782578992378</v>
       </c>
       <c r="BM21" t="n">
         <v>2366.471</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28291, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ORBKdj9n/", "exitScreenshotUrl": "https://www.tradingview.com/x/VrYgZMka/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2363.241, "sourceLowPrice": 2357.5}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28291, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ORBKdj9n/", "exitScreenshotUrl": "https://www.tradingview.com/x/VrYgZMka/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2363.241, "sourceLowPrice": 2357.5, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
@@ -11839,7 +11839,7 @@
         <v>34</v>
       </c>
       <c r="BL22" t="n">
-        <v>1782575585785</v>
+        <v>1782578992378</v>
       </c>
       <c r="BM22" t="n">
         <v>2366.151</v>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28275, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/pXXTLeLm/", "exitScreenshotUrl": "https://www.tradingview.com/x/qiPyN0UP/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2346.219, "sourceLowPrice": 2341.6}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28275, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/pXXTLeLm/", "exitScreenshotUrl": "https://www.tradingview.com/x/qiPyN0UP/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2346.219, "sourceLowPrice": 2341.6, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
@@ -12363,7 +12363,7 @@
         <v>34</v>
       </c>
       <c r="BL23" t="n">
-        <v>1782575585785</v>
+        <v>1782578992378</v>
       </c>
       <c r="BM23" t="n">
         <v>2348.369</v>
@@ -12832,7 +12832,7 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28282, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/pXz2il84/", "exitScreenshotUrl": "https://www.tradingview.com/x/GMPdgWPs/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2337.54, "sourceLowPrice": 2332.695}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28282, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/pXz2il84/", "exitScreenshotUrl": "https://www.tradingview.com/x/GMPdgWPs/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2337.54, "sourceLowPrice": 2332.695, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
@@ -12887,7 +12887,7 @@
         <v>34</v>
       </c>
       <c r="BL24" t="n">
-        <v>1782575585786</v>
+        <v>1782578992378</v>
       </c>
       <c r="BM24" t="n">
         <v>2337.043</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28294, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/hCST1I6h/", "exitScreenshotUrl": "https://www.tradingview.com/x/6NCvuodm/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2343.64, "sourceLowPrice": 2340.0}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28294, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/hCST1I6h/", "exitScreenshotUrl": "https://www.tradingview.com/x/6NCvuodm/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2343.64, "sourceLowPrice": 2340.0, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
@@ -13411,7 +13411,7 @@
         <v>34</v>
       </c>
       <c r="BL25" t="n">
-        <v>1782575585786</v>
+        <v>1782578992379</v>
       </c>
       <c r="BM25" t="n">
         <v>2338.4</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28281, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/y7dwa5mf/", "exitScreenshotUrl": "https://www.tradingview.com/x/GMu636ia/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2355.591, "sourceLowPrice": 2346.1}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28281, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/y7dwa5mf/", "exitScreenshotUrl": "https://www.tradingview.com/x/GMu636ia/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2355.591, "sourceLowPrice": 2346.1, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
@@ -13935,7 +13935,7 @@
         <v>34</v>
       </c>
       <c r="BL26" t="n">
-        <v>1782575585786</v>
+        <v>1782578992379</v>
       </c>
       <c r="BM26" t="n">
         <v>2349.026</v>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28319, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/nzdOGiVZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/Yl8oNeA6/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2369.71, "sourceLowPrice": 2364.4}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28319, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/nzdOGiVZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/Yl8oNeA6/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2369.71, "sourceLowPrice": 2364.4, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
@@ -14459,7 +14459,7 @@
         <v>34</v>
       </c>
       <c r="BL27" t="n">
-        <v>1782575585787</v>
+        <v>1782578992379</v>
       </c>
       <c r="BM27" t="n">
         <v>2363.004</v>
@@ -14928,7 +14928,7 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28284, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/32Rd6KK1/", "exitScreenshotUrl": "https://www.tradingview.com/x/fGAzHaWE/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2374.26, "sourceLowPrice": 2369.9}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28284, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/32Rd6KK1/", "exitScreenshotUrl": "https://www.tradingview.com/x/fGAzHaWE/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2374.26, "sourceLowPrice": 2369.9, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
@@ -14983,7 +14983,7 @@
         <v>34</v>
       </c>
       <c r="BL28" t="n">
-        <v>1782575585787</v>
+        <v>1782578992379</v>
       </c>
       <c r="BM28" t="n">
         <v>2370.221</v>
@@ -15452,7 +15452,7 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28320, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/tKKMkLiP/", "exitScreenshotUrl": "https://www.tradingview.com/x/x8unseOM/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2388.71, "sourceLowPrice": 2381.945}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28320, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/tKKMkLiP/", "exitScreenshotUrl": "https://www.tradingview.com/x/x8unseOM/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2388.71, "sourceLowPrice": 2381.945, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
@@ -15507,7 +15507,7 @@
         <v>34</v>
       </c>
       <c r="BL29" t="n">
-        <v>1782575585787</v>
+        <v>1782578992379</v>
       </c>
       <c r="BM29" t="n">
         <v>2380.714</v>
@@ -15701,7 +15701,7 @@
       </c>
       <c r="DO29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 2380.714, "new": 2380.281, "at": 1715771940000}]</t>
         </is>
       </c>
       <c r="DP29" t="n">
@@ -15976,7 +15976,7 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 10422, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/TgJ4YuPz/", "exitScreenshotUrl": "https://www.tradingview.com/x/6VnZ6rzy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2388.13, "sourceLowPrice": 2385.3}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 10422, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/TgJ4YuPz/", "exitScreenshotUrl": "https://www.tradingview.com/x/6VnZ6rzy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2388.13, "sourceLowPrice": 2385.3, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
@@ -16031,7 +16031,7 @@
         <v>34</v>
       </c>
       <c r="BL30" t="n">
-        <v>1782575585788</v>
+        <v>1782578992379</v>
       </c>
       <c r="BM30" t="n">
         <v>2389.744</v>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 25102, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/zibMbKss/", "exitScreenshotUrl": "https://www.tradingview.com/x/FPBkTWDv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2382.37, "sourceLowPrice": 2379.025}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 25102, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/zibMbKss/", "exitScreenshotUrl": "https://www.tradingview.com/x/FPBkTWDv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2382.37, "sourceLowPrice": 2379.025, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
@@ -16555,7 +16555,7 @@
         <v>34</v>
       </c>
       <c r="BL31" t="n">
-        <v>1782575585788</v>
+        <v>1782578992380</v>
       </c>
       <c r="BM31" t="n">
         <v>2379.025</v>
@@ -17024,7 +17024,7 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28285, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ICDiOLLn/", "exitScreenshotUrl": "https://www.tradingview.com/x/HwOj1Eue/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2383.801, "sourceLowPrice": 2379.6}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28285, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ICDiOLLn/", "exitScreenshotUrl": "https://www.tradingview.com/x/HwOj1Eue/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2383.801, "sourceLowPrice": 2379.6, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
@@ -17079,7 +17079,7 @@
         <v>34</v>
       </c>
       <c r="BL32" t="n">
-        <v>1782575585789</v>
+        <v>1782578992380</v>
       </c>
       <c r="BM32" t="n">
         <v>2380.195</v>
@@ -17548,7 +17548,7 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28343, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/L5xp9Up9/", "exitScreenshotUrl": "https://www.tradingview.com/x/HAPE9Aeg/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2384.65, "sourceLowPrice": 2381.7}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28343, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/L5xp9Up9/", "exitScreenshotUrl": "https://www.tradingview.com/x/HAPE9Aeg/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2384.65, "sourceLowPrice": 2381.7, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
@@ -17603,7 +17603,7 @@
         <v>34</v>
       </c>
       <c r="BL33" t="n">
-        <v>1782575585789</v>
+        <v>1782578992380</v>
       </c>
       <c r="BM33" t="n">
         <v>2384.366</v>
@@ -18072,7 +18072,7 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28303, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/uK3Yslei/", "exitScreenshotUrl": "https://www.tradingview.com/x/HxzjypGM/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2385.5, "sourceLowPrice": 2381.1}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28303, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/uK3Yslei/", "exitScreenshotUrl": "https://www.tradingview.com/x/HxzjypGM/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2385.5, "sourceLowPrice": 2381.1, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
@@ -18127,7 +18127,7 @@
         <v>34</v>
       </c>
       <c r="BL34" t="n">
-        <v>1782575585789</v>
+        <v>1782578992380</v>
       </c>
       <c r="BM34" t="n">
         <v>2383.578</v>
@@ -18596,7 +18596,7 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28344, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MBCGmRhD/", "exitScreenshotUrl": "https://www.tradingview.com/x/NNnEgkpc/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2409.62, "sourceLowPrice": 2403.123}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28344, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MBCGmRhD/", "exitScreenshotUrl": "https://www.tradingview.com/x/NNnEgkpc/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2409.62, "sourceLowPrice": 2403.123, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
@@ -18651,7 +18651,7 @@
         <v>34</v>
       </c>
       <c r="BL35" t="n">
-        <v>1782575585790</v>
+        <v>1782578992380</v>
       </c>
       <c r="BM35" t="n">
         <v>2401.61</v>
@@ -18845,7 +18845,7 @@
       </c>
       <c r="DO35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 2401.61, "new": 2400.863, "at": 1715941680000}]</t>
         </is>
       </c>
       <c r="DP35" t="n">
@@ -19120,7 +19120,7 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28326, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/iUr4W7dl/", "exitScreenshotUrl": "https://www.tradingview.com/x/cbv2i0tm/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2414.938, "sourceLowPrice": 2410.495}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28326, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/iUr4W7dl/", "exitScreenshotUrl": "https://www.tradingview.com/x/cbv2i0tm/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2414.938, "sourceLowPrice": 2410.495, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
@@ -19175,7 +19175,7 @@
         <v>34</v>
       </c>
       <c r="BL36" t="n">
-        <v>1782575585790</v>
+        <v>1782578992381</v>
       </c>
       <c r="BM36" t="n">
         <v>2411.41</v>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28347, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/kGjra2LJ/", "exitScreenshotUrl": "https://www.tradingview.com/x/MrgHQkXb/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2426.96, "sourceLowPrice": 2421.3}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28347, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/kGjra2LJ/", "exitScreenshotUrl": "https://www.tradingview.com/x/MrgHQkXb/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2426.96, "sourceLowPrice": 2421.3, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
@@ -19699,7 +19699,7 @@
         <v>34</v>
       </c>
       <c r="BL37" t="n">
-        <v>1782575585791</v>
+        <v>1782578992381</v>
       </c>
       <c r="BM37" t="n">
         <v>2419.664</v>
@@ -20168,7 +20168,7 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28305, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/bmDKObH1/", "exitScreenshotUrl": "https://www.tradingview.com/x/AD9ws3Du/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2428.13, "sourceLowPrice": 2423.9}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28305, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/bmDKObH1/", "exitScreenshotUrl": "https://www.tradingview.com/x/AD9ws3Du/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2428.13, "sourceLowPrice": 2423.9, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
@@ -20223,7 +20223,7 @@
         <v>34</v>
       </c>
       <c r="BL38" t="n">
-        <v>1782575585791</v>
+        <v>1782578992381</v>
       </c>
       <c r="BM38" t="n">
         <v>2424.568</v>
@@ -20692,7 +20692,7 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28309, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/tjvtghMK/", "exitScreenshotUrl": "https://www.tradingview.com/x/E05lSpSS/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2420.21, "sourceLowPrice": 2416.768}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28309, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/tjvtghMK/", "exitScreenshotUrl": "https://www.tradingview.com/x/E05lSpSS/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2420.21, "sourceLowPrice": 2416.768, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
@@ -20747,7 +20747,7 @@
         <v>34</v>
       </c>
       <c r="BL39" t="n">
-        <v>1782575585792</v>
+        <v>1782578992381</v>
       </c>
       <c r="BM39" t="n">
         <v>2415.056</v>
@@ -21216,7 +21216,7 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28361, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/s41YegAx/", "exitScreenshotUrl": "https://www.tradingview.com/x/M7aa6gXW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2425.58, "sourceLowPrice": 2419.915}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28361, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/s41YegAx/", "exitScreenshotUrl": "https://www.tradingview.com/x/M7aa6gXW/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2425.58, "sourceLowPrice": 2419.915, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
@@ -21271,7 +21271,7 @@
         <v>34</v>
       </c>
       <c r="BL40" t="n">
-        <v>1782575585792</v>
+        <v>1782578992381</v>
       </c>
       <c r="BM40" t="n">
         <v>2427.893</v>
@@ -21465,7 +21465,7 @@
       </c>
       <c r="DO40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 2427.893, "new": 2428.587, "at": 1716291900000}]</t>
         </is>
       </c>
       <c r="DP40" t="n">
@@ -21740,7 +21740,7 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 25084, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/PXdQt6m7/", "exitScreenshotUrl": "https://www.tradingview.com/x/A1Pf3UEQ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2423.637, "sourceLowPrice": 2418.036}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 25084, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/PXdQt6m7/", "exitScreenshotUrl": "https://www.tradingview.com/x/A1Pf3UEQ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "missed-trade", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2423.637, "sourceLowPrice": 2418.036, "rule_outcome": "missed", "reason": "Missed trade", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
@@ -21795,7 +21795,7 @@
         <v>34</v>
       </c>
       <c r="BL41" t="n">
-        <v>1782575585793</v>
+        <v>1782578992381</v>
       </c>
       <c r="BM41" t="n">
         <v>2423.637</v>
@@ -21976,11 +21976,11 @@
       </c>
       <c r="DL41" t="inlineStr">
         <is>
-          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "missed-trade"}</t>
         </is>
       </c>
       <c r="DM41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN41" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
       </c>
       <c r="EF41" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>missed-trade</t>
         </is>
       </c>
       <c r="EG41" t="inlineStr">
@@ -22264,7 +22264,7 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28398, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/rspfdAcC/", "exitScreenshotUrl": "https://www.tradingview.com/x/mt4z58Yz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2416.08, "sourceLowPrice": 2411.894}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28398, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/rspfdAcC/", "exitScreenshotUrl": "https://www.tradingview.com/x/mt4z58Yz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2416.08, "sourceLowPrice": 2411.894, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
@@ -22319,7 +22319,7 @@
         <v>34</v>
       </c>
       <c r="BL42" t="n">
-        <v>1782575585793</v>
+        <v>1782578992382</v>
       </c>
       <c r="BM42" t="n">
         <v>2417.541</v>
@@ -22788,7 +22788,7 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28380, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/jPmwJyKa/", "exitScreenshotUrl": "https://www.tradingview.com/x/MVt3O4L0/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2415.65, "sourceLowPrice": 2410.2}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28380, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/jPmwJyKa/", "exitScreenshotUrl": "https://www.tradingview.com/x/MVt3O4L0/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2415.65, "sourceLowPrice": 2410.2, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
@@ -22843,7 +22843,7 @@
         <v>34</v>
       </c>
       <c r="BL43" t="n">
-        <v>1782575585793</v>
+        <v>1782578992382</v>
       </c>
       <c r="BM43" t="n">
         <v>2413.739</v>
@@ -23037,7 +23037,7 @@
       </c>
       <c r="DO43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 2413.739, "new": 2414.193, "at": 1716352020000}]</t>
         </is>
       </c>
       <c r="DP43" t="n">
@@ -23312,7 +23312,7 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28400, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/assbqjVd/", "exitScreenshotUrl": "https://www.tradingview.com/x/orBIDQgd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2408.7, "sourceLowPrice": 2401.015}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28400, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/assbqjVd/", "exitScreenshotUrl": "https://www.tradingview.com/x/orBIDQgd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2408.7, "sourceLowPrice": 2401.015, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
@@ -23367,7 +23367,7 @@
         <v>34</v>
       </c>
       <c r="BL44" t="n">
-        <v>1782575585794</v>
+        <v>1782578992382</v>
       </c>
       <c r="BM44" t="n">
         <v>2411.821</v>
@@ -23378,7 +23378,7 @@
         </is>
       </c>
       <c r="BO44" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="BP44" t="n">
         <v>1</v>
@@ -23836,7 +23836,7 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28383, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/TlBtlHQl/", "exitScreenshotUrl": "https://www.tradingview.com/x/He2fJFzE/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2353.33, "sourceLowPrice": 2342.108}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28383, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/TlBtlHQl/", "exitScreenshotUrl": "https://www.tradingview.com/x/He2fJFzE/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2353.33, "sourceLowPrice": 2342.108, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
@@ -23891,7 +23891,7 @@
         <v>34</v>
       </c>
       <c r="BL45" t="n">
-        <v>1782575585794</v>
+        <v>1782578992382</v>
       </c>
       <c r="BM45" t="n">
         <v>2356.465</v>
@@ -24360,7 +24360,7 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28451, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/fmFH7lgc/", "exitScreenshotUrl": "https://www.tradingview.com/x/4wnJCJcj/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2348.07, "sourceLowPrice": 2341.415}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28451, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/fmFH7lgc/", "exitScreenshotUrl": "https://www.tradingview.com/x/4wnJCJcj/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2348.07, "sourceLowPrice": 2341.415, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
@@ -24415,7 +24415,7 @@
         <v>34</v>
       </c>
       <c r="BL46" t="n">
-        <v>1782575585794</v>
+        <v>1782578992382</v>
       </c>
       <c r="BM46" t="n">
         <v>2347.28</v>
@@ -24884,7 +24884,7 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28401, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/fXhUosPt/", "exitScreenshotUrl": "https://www.tradingview.com/x/5Ce2fpJY/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2347.68, "sourceLowPrice": 2339.9}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28401, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/fXhUosPt/", "exitScreenshotUrl": "https://www.tradingview.com/x/5Ce2fpJY/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2347.68, "sourceLowPrice": 2339.9, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
@@ -24939,7 +24939,7 @@
         <v>34</v>
       </c>
       <c r="BL47" t="n">
-        <v>1782575585795</v>
+        <v>1782578992382</v>
       </c>
       <c r="BM47" t="n">
         <v>2344.78</v>
@@ -25120,11 +25120,11 @@
       </c>
       <c r="DL47" t="inlineStr">
         <is>
-          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN47" t="inlineStr">
         <is>
@@ -25198,12 +25198,12 @@
       </c>
       <c r="EF47" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "overtrade", "label": "Overtrading", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 1000, "evidence": "Took an extra trade outside the planned session window.", "detected_at": "2024-05-23T11:38:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH47" t="inlineStr">
@@ -25408,7 +25408,7 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28452, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/krBAFB1m/", "exitScreenshotUrl": "https://www.tradingview.com/x/RJA1llHF/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2345.82, "sourceLowPrice": 2342.6}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28452, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/krBAFB1m/", "exitScreenshotUrl": "https://www.tradingview.com/x/RJA1llHF/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2345.82, "sourceLowPrice": 2342.6, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
@@ -25463,7 +25463,7 @@
         <v>34</v>
       </c>
       <c r="BL48" t="n">
-        <v>1782575585795</v>
+        <v>1782578992382</v>
       </c>
       <c r="BM48" t="n">
         <v>2348.029</v>
@@ -25932,7 +25932,7 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28439, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/mTQ5fzDU/", "exitScreenshotUrl": "https://www.tradingview.com/x/BwzMNgdI/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2343.16, "sourceLowPrice": 2337.521}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28439, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/mTQ5fzDU/", "exitScreenshotUrl": "https://www.tradingview.com/x/BwzMNgdI/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2343.16, "sourceLowPrice": 2337.521, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
@@ -25987,7 +25987,7 @@
         <v>34</v>
       </c>
       <c r="BL49" t="n">
-        <v>1782575585795</v>
+        <v>1782578992383</v>
       </c>
       <c r="BM49" t="n">
         <v>2343.969</v>
@@ -26456,7 +26456,7 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28472, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/uPHTs20o/", "exitScreenshotUrl": "https://www.tradingview.com/x/g1bYHu8m/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2343.26, "sourceLowPrice": 2339.0}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28472, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/uPHTs20o/", "exitScreenshotUrl": "https://www.tradingview.com/x/g1bYHu8m/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2343.26, "sourceLowPrice": 2339.0, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
@@ -26511,7 +26511,7 @@
         <v>34</v>
       </c>
       <c r="BL50" t="n">
-        <v>1782575585796</v>
+        <v>1782578992383</v>
       </c>
       <c r="BM50" t="n">
         <v>2337.841</v>
@@ -26980,7 +26980,7 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28407, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/R1kZi7FP/", "exitScreenshotUrl": "https://www.tradingview.com/x/nA7AQSSf/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2358.55, "sourceLowPrice": 2353.8}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28407, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/R1kZi7FP/", "exitScreenshotUrl": "https://www.tradingview.com/x/nA7AQSSf/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2358.55, "sourceLowPrice": 2353.8, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
@@ -27035,7 +27035,7 @@
         <v>34</v>
       </c>
       <c r="BL51" t="n">
-        <v>1782575585796</v>
+        <v>1782578992383</v>
       </c>
       <c r="BM51" t="n">
         <v>2354.618</v>
@@ -27504,7 +27504,7 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28413, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/muxsvy8d/", "exitScreenshotUrl": "https://www.tradingview.com/x/zTnMQWmo/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2342.45, "sourceLowPrice": 2339.9}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28413, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/muxsvy8d/", "exitScreenshotUrl": "https://www.tradingview.com/x/zTnMQWmo/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2342.45, "sourceLowPrice": 2339.9, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
@@ -27559,7 +27559,7 @@
         <v>34</v>
       </c>
       <c r="BL52" t="n">
-        <v>1782575585797</v>
+        <v>1782578992383</v>
       </c>
       <c r="BM52" t="n">
         <v>2344.241</v>
@@ -28028,7 +28028,7 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28414, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MrQRHkXV/", "exitScreenshotUrl": "https://www.tradingview.com/x/Tmt2tr70/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2362.22, "sourceLowPrice": 2356.975}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28414, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MrQRHkXV/", "exitScreenshotUrl": "https://www.tradingview.com/x/Tmt2tr70/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2362.22, "sourceLowPrice": 2356.975, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
@@ -28083,7 +28083,7 @@
         <v>34</v>
       </c>
       <c r="BL53" t="n">
-        <v>1782575585797</v>
+        <v>1782578992383</v>
       </c>
       <c r="BM53" t="n">
         <v>2357.151</v>
@@ -28264,11 +28264,11 @@
       </c>
       <c r="DL53" t="inlineStr">
         <is>
-          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN53" t="inlineStr">
         <is>
@@ -28342,12 +28342,12 @@
       </c>
       <c r="EF53" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "size_up", "label": "Size Up", "source": "manual", "state": "confirmed", "cost_R": 1.0, "cost_$": 1000, "evidence": "Position size exceeded the planned risk envelope.", "detected_at": "2024-05-28T12:27:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH53" t="inlineStr">
@@ -28552,7 +28552,7 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28489, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MWh0WoFm/", "exitScreenshotUrl": "https://www.tradingview.com/x/FJQ4skxz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2351.74, "sourceLowPrice": 2346.4}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28489, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MWh0WoFm/", "exitScreenshotUrl": "https://www.tradingview.com/x/FJQ4skxz/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2351.74, "sourceLowPrice": 2346.4, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
@@ -28607,7 +28607,7 @@
         <v>34</v>
       </c>
       <c r="BL54" t="n">
-        <v>1782575585798</v>
+        <v>1782578992383</v>
       </c>
       <c r="BM54" t="n">
         <v>2352.036</v>
@@ -29076,7 +29076,7 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28415, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/NKfR7qqN/", "exitScreenshotUrl": "https://www.tradingview.com/x/bIs06qwO/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2348.41, "sourceLowPrice": 2343.3}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28415, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/NKfR7qqN/", "exitScreenshotUrl": "https://www.tradingview.com/x/bIs06qwO/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2348.41, "sourceLowPrice": 2343.3, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
@@ -29131,7 +29131,7 @@
         <v>34</v>
       </c>
       <c r="BL55" t="n">
-        <v>1782575585798</v>
+        <v>1782578992384</v>
       </c>
       <c r="BM55" t="n">
         <v>2348.595</v>
@@ -29600,7 +29600,7 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28442, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MbmVODUl/", "exitScreenshotUrl": "https://www.tradingview.com/x/sumfM4mg/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2341.574, "sourceLowPrice": 2337.965}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28442, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MbmVODUl/", "exitScreenshotUrl": "https://www.tradingview.com/x/sumfM4mg/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2341.574, "sourceLowPrice": 2337.965, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
@@ -29655,7 +29655,7 @@
         <v>34</v>
       </c>
       <c r="BL56" t="n">
-        <v>1782575585799</v>
+        <v>1782578992384</v>
       </c>
       <c r="BM56" t="n">
         <v>2341.574</v>
@@ -29836,11 +29836,11 @@
       </c>
       <c r="DL56" t="inlineStr">
         <is>
-          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN56" t="inlineStr">
         <is>
@@ -29914,12 +29914,12 @@
       </c>
       <c r="EF56" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "fomo", "label": "FOMO", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 1000, "evidence": "Entered after the move was already extended without a fresh setup.", "detected_at": "2024-05-29T11:52:00.000Z"}, {"type": "late_entry", "label": "Late Entry", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 1000, "evidence": "Entered after the optimal entry window had passed.", "detected_at": "2024-05-29T11:52:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH56" t="inlineStr">
@@ -30124,7 +30124,7 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28476, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/aFbl3DZW/", "exitScreenshotUrl": "https://www.tradingview.com/x/4NLZ4ALZ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2338.683, "sourceLowPrice": 2336.403}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28476, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/aFbl3DZW/", "exitScreenshotUrl": "https://www.tradingview.com/x/4NLZ4ALZ/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2338.683, "sourceLowPrice": 2336.403, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
@@ -30179,7 +30179,7 @@
         <v>34</v>
       </c>
       <c r="BL57" t="n">
-        <v>1782575585799</v>
+        <v>1782578992384</v>
       </c>
       <c r="BM57" t="n">
         <v>2338.683</v>
@@ -30360,11 +30360,11 @@
       </c>
       <c r="DL57" t="inlineStr">
         <is>
-          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN57" t="inlineStr">
         <is>
@@ -30438,12 +30438,12 @@
       </c>
       <c r="EF57" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "overtrade", "label": "Overtrading", "source": "manual", "state": "confirmed", "cost_R": 1.0, "cost_$": 1000, "evidence": "Took an extra trade outside the planned session window.", "detected_at": "2024-05-29T12:22:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH57" t="inlineStr">
@@ -30648,7 +30648,7 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28601, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/jWyxiTLq/", "exitScreenshotUrl": "https://www.tradingview.com/x/KMexMt0G/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2335.11, "sourceLowPrice": 2331.6}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28601, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/jWyxiTLq/", "exitScreenshotUrl": "https://www.tradingview.com/x/KMexMt0G/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2335.11, "sourceLowPrice": 2331.6, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
@@ -30703,7 +30703,7 @@
         <v>34</v>
       </c>
       <c r="BL58" t="n">
-        <v>1782575585800</v>
+        <v>1782578992384</v>
       </c>
       <c r="BM58" t="n">
         <v>2334.782</v>
@@ -31172,7 +31172,7 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28579, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AlB5cCxm/", "exitScreenshotUrl": "https://www.tradingview.com/x/cQow1s0x/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2351.82, "sourceLowPrice": 2346.6}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28579, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AlB5cCxm/", "exitScreenshotUrl": "https://www.tradingview.com/x/cQow1s0x/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2351.82, "sourceLowPrice": 2346.6, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
@@ -31227,7 +31227,7 @@
         <v>34</v>
       </c>
       <c r="BL59" t="n">
-        <v>1782575585800</v>
+        <v>1782578992384</v>
       </c>
       <c r="BM59" t="n">
         <v>2344.647</v>
@@ -31421,7 +31421,7 @@
       </c>
       <c r="DO59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 2344.647, "new": 2343.818, "at": 1717063380000}]</t>
         </is>
       </c>
       <c r="DP59" t="n">
@@ -31696,7 +31696,7 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28604, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ZhIV3QS1/", "exitScreenshotUrl": "https://www.tradingview.com/x/mPGQ8Iz9/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2338.22, "sourceLowPrice": 2329.3}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28604, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/ZhIV3QS1/", "exitScreenshotUrl": "https://www.tradingview.com/x/mPGQ8Iz9/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2338.22, "sourceLowPrice": 2329.3, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
@@ -31751,7 +31751,7 @@
         <v>34</v>
       </c>
       <c r="BL60" t="n">
-        <v>1782575585801</v>
+        <v>1782578992384</v>
       </c>
       <c r="BM60" t="n">
         <v>2341.421</v>
@@ -31945,7 +31945,7 @@
       </c>
       <c r="DO60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 2341.421, "new": 2342.545, "at": 1717065660000}]</t>
         </is>
       </c>
       <c r="DP60" t="n">
@@ -32220,7 +32220,7 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28658, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9cR212Zy/", "exitScreenshotUrl": "https://www.tradingview.com/x/gceUW4oY/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2334.67, "sourceLowPrice": 2327.635}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28658, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9cR212Zy/", "exitScreenshotUrl": "https://www.tradingview.com/x/gceUW4oY/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2334.67, "sourceLowPrice": 2327.635, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
@@ -32275,7 +32275,7 @@
         <v>34</v>
       </c>
       <c r="BL61" t="n">
-        <v>1782575585801</v>
+        <v>1782578992385</v>
       </c>
       <c r="BM61" t="n">
         <v>2336.327</v>
@@ -32744,7 +32744,7 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28605, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/OF3gWNl2/", "exitScreenshotUrl": "https://www.tradingview.com/x/ddRCBEa4/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2336.69, "sourceLowPrice": 2331.8}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28605, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/OF3gWNl2/", "exitScreenshotUrl": "https://www.tradingview.com/x/ddRCBEa4/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2336.69, "sourceLowPrice": 2331.8, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
@@ -32799,7 +32799,7 @@
         <v>34</v>
       </c>
       <c r="BL62" t="n">
-        <v>1782575585802</v>
+        <v>1782578992385</v>
       </c>
       <c r="BM62" t="n">
         <v>2333.797</v>
@@ -33268,7 +33268,7 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28595, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/DyvsWt23/", "exitScreenshotUrl": "https://www.tradingview.com/x/u3ZVecEf/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2328.53, "sourceLowPrice": 2324.1}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28595, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/DyvsWt23/", "exitScreenshotUrl": "https://www.tradingview.com/x/u3ZVecEf/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2328.53, "sourceLowPrice": 2324.1, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
@@ -33323,7 +33323,7 @@
         <v>34</v>
       </c>
       <c r="BL63" t="n">
-        <v>1782575585802</v>
+        <v>1782578992385</v>
       </c>
       <c r="BM63" t="n">
         <v>2324.387</v>
@@ -33334,7 +33334,7 @@
         </is>
       </c>
       <c r="BO63" t="n">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="BP63" t="n">
         <v>1</v>
@@ -33792,7 +33792,7 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28620, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/0tRURqTb/", "exitScreenshotUrl": "https://www.tradingview.com/x/x886IDNy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2345.24, "sourceLowPrice": 2335.1}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28620, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/0tRURqTb/", "exitScreenshotUrl": "https://www.tradingview.com/x/x886IDNy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2345.24, "sourceLowPrice": 2335.1, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
@@ -33847,7 +33847,7 @@
         <v>34</v>
       </c>
       <c r="BL64" t="n">
-        <v>1782575585803</v>
+        <v>1782578992385</v>
       </c>
       <c r="BM64" t="n">
         <v>2337.982</v>
@@ -33858,7 +33858,7 @@
         </is>
       </c>
       <c r="BO64" t="n">
-        <v>1</v>
+        <v>1.46</v>
       </c>
       <c r="BP64" t="n">
         <v>1</v>
@@ -34316,7 +34316,7 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28661, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/3D37aPmg/", "exitScreenshotUrl": "https://www.tradingview.com/x/S64dm61o/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2349.0, "sourceLowPrice": 2345.0}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28661, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/3D37aPmg/", "exitScreenshotUrl": "https://www.tradingview.com/x/S64dm61o/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2349.0, "sourceLowPrice": 2345.0, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
@@ -34371,7 +34371,7 @@
         <v>34</v>
       </c>
       <c r="BL65" t="n">
-        <v>1782575585803</v>
+        <v>1782578992385</v>
       </c>
       <c r="BM65" t="n">
         <v>2343.37</v>
@@ -34840,7 +34840,7 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28641, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/w46rEdJQ/", "exitScreenshotUrl": "https://www.tradingview.com/x/hqVNU3N3/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2336.0, "sourceLowPrice": 2330.7}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28641, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/w46rEdJQ/", "exitScreenshotUrl": "https://www.tradingview.com/x/hqVNU3N3/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2336.0, "sourceLowPrice": 2330.7, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
@@ -34895,7 +34895,7 @@
         <v>34</v>
       </c>
       <c r="BL66" t="n">
-        <v>1782575585805</v>
+        <v>1782578992386</v>
       </c>
       <c r="BM66" t="n">
         <v>2336.995</v>
@@ -35364,7 +35364,7 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28662, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MHUOR8gb/", "exitScreenshotUrl": "https://www.tradingview.com/x/bLPpS3XK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2321.949, "sourceLowPrice": 2315.704}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28662, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/MHUOR8gb/", "exitScreenshotUrl": "https://www.tradingview.com/x/bLPpS3XK/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2321.949, "sourceLowPrice": 2315.704, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
@@ -35419,7 +35419,7 @@
         <v>34</v>
       </c>
       <c r="BL67" t="n">
-        <v>1782575585805</v>
+        <v>1782578992386</v>
       </c>
       <c r="BM67" t="n">
         <v>2326.819</v>
@@ -35888,7 +35888,7 @@
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28642, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/bqoChwTO/", "exitScreenshotUrl": "https://www.tradingview.com/x/98gZi68e/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2329.65, "sourceLowPrice": 2324.6}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28642, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/bqoChwTO/", "exitScreenshotUrl": "https://www.tradingview.com/x/98gZi68e/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2329.65, "sourceLowPrice": 2324.6, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
@@ -35943,7 +35943,7 @@
         <v>34</v>
       </c>
       <c r="BL68" t="n">
-        <v>1782575585805</v>
+        <v>1782578992386</v>
       </c>
       <c r="BM68" t="n">
         <v>2326.026</v>
@@ -36412,7 +36412,7 @@
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28606, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AU51CmFt/", "exitScreenshotUrl": "https://www.tradingview.com/x/H9JG4CXS/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2335.11, "sourceLowPrice": 2331.5}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28606, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AU51CmFt/", "exitScreenshotUrl": "https://www.tradingview.com/x/H9JG4CXS/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2335.11, "sourceLowPrice": 2331.5, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
@@ -36467,7 +36467,7 @@
         <v>34</v>
       </c>
       <c r="BL69" t="n">
-        <v>1782575585806</v>
+        <v>1782578992386</v>
       </c>
       <c r="BM69" t="n">
         <v>2331.701</v>
@@ -36478,7 +36478,7 @@
         </is>
       </c>
       <c r="BO69" t="n">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="BP69" t="n">
         <v>1</v>
@@ -36936,7 +36936,7 @@
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28622, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/UXEwWABV/", "exitScreenshotUrl": "https://www.tradingview.com/x/hMS4FOY1/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2352.711, "sourceLowPrice": 2343.7}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28622, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/UXEwWABV/", "exitScreenshotUrl": "https://www.tradingview.com/x/hMS4FOY1/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "missed-trade", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2352.711, "sourceLowPrice": 2343.7, "rule_outcome": "missed", "reason": "Missed trade", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
@@ -36991,7 +36991,7 @@
         <v>34</v>
       </c>
       <c r="BL70" t="n">
-        <v>1782575585806</v>
+        <v>1782578992386</v>
       </c>
       <c r="BM70" t="n">
         <v>2340.627</v>
@@ -37172,11 +37172,11 @@
       </c>
       <c r="DL70" t="inlineStr">
         <is>
-          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "missed-trade"}</t>
         </is>
       </c>
       <c r="DM70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN70" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         </is>
       </c>
       <c r="EC70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ED70" t="n">
         <v>2024</v>
@@ -37250,7 +37250,7 @@
       </c>
       <c r="EF70" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>missed-trade</t>
         </is>
       </c>
       <c r="EG70" t="inlineStr">
@@ -37460,7 +37460,7 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28623, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/IvQxoxe5/", "exitScreenshotUrl": "https://www.tradingview.com/x/X2FD5z5o/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2354.09, "sourceLowPrice": 2349.51}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28623, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/IvQxoxe5/", "exitScreenshotUrl": "https://www.tradingview.com/x/X2FD5z5o/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2354.09, "sourceLowPrice": 2349.51, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
@@ -37515,7 +37515,7 @@
         <v>34</v>
       </c>
       <c r="BL71" t="n">
-        <v>1782575585807</v>
+        <v>1782578992386</v>
       </c>
       <c r="BM71" t="n">
         <v>2347.068</v>
@@ -37984,7 +37984,7 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28607, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9W1fTQuq/", "exitScreenshotUrl": "https://www.tradingview.com/x/ViSl8TNr/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2357.34, "sourceLowPrice": 2353.6}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28607, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9W1fTQuq/", "exitScreenshotUrl": "https://www.tradingview.com/x/ViSl8TNr/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2357.34, "sourceLowPrice": 2353.6, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
@@ -38039,7 +38039,7 @@
         <v>34</v>
       </c>
       <c r="BL72" t="n">
-        <v>1782575585807</v>
+        <v>1782578992387</v>
       </c>
       <c r="BM72" t="n">
         <v>2351.395</v>
@@ -38508,7 +38508,7 @@
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28609, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AZAPIngv/", "exitScreenshotUrl": "https://www.tradingview.com/x/n7hVFF23/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2363.03, "sourceLowPrice": 2359.6}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28609, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AZAPIngv/", "exitScreenshotUrl": "https://www.tradingview.com/x/n7hVFF23/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2363.03, "sourceLowPrice": 2359.6, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
@@ -38563,7 +38563,7 @@
         <v>34</v>
       </c>
       <c r="BL73" t="n">
-        <v>1782575585807</v>
+        <v>1782578992387</v>
       </c>
       <c r="BM73" t="n">
         <v>2363.688</v>
@@ -39032,7 +39032,7 @@
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28665, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/4FhomDYt/", "exitScreenshotUrl": "https://www.tradingview.com/x/Z2hSwYHj/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2363.19, "sourceLowPrice": 2360.5}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28665, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/4FhomDYt/", "exitScreenshotUrl": "https://www.tradingview.com/x/Z2hSwYHj/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2363.19, "sourceLowPrice": 2360.5, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
@@ -39087,7 +39087,7 @@
         <v>34</v>
       </c>
       <c r="BL74" t="n">
-        <v>1782575585808</v>
+        <v>1782578992387</v>
       </c>
       <c r="BM74" t="n">
         <v>2362.593</v>
@@ -39098,7 +39098,7 @@
         </is>
       </c>
       <c r="BO74" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="BP74" t="n">
         <v>1</v>
@@ -39556,7 +39556,7 @@
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28667, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/20nVepz9/", "exitScreenshotUrl": "https://www.tradingview.com/x/FmQoAF4O/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2371.86, "sourceLowPrice": 2366.2}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28667, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/20nVepz9/", "exitScreenshotUrl": "https://www.tradingview.com/x/FmQoAF4O/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2371.86, "sourceLowPrice": 2366.2, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
@@ -39611,7 +39611,7 @@
         <v>34</v>
       </c>
       <c r="BL75" t="n">
-        <v>1782575585808</v>
+        <v>1782578992387</v>
       </c>
       <c r="BM75" t="n">
         <v>2364.129</v>
@@ -39792,11 +39792,11 @@
       </c>
       <c r="DL75" t="inlineStr">
         <is>
-          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN75" t="inlineStr">
         <is>
@@ -39870,7 +39870,7 @@
       </c>
       <c r="EF75" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG75" t="inlineStr">
@@ -40080,7 +40080,7 @@
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28598, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/3hfCYyY0/", "exitScreenshotUrl": "https://www.tradingview.com/x/j54VUu1O/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2377.761, "sourceLowPrice": 2371.1}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28598, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/3hfCYyY0/", "exitScreenshotUrl": "https://www.tradingview.com/x/j54VUu1O/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2377.761, "sourceLowPrice": 2371.1, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
@@ -40135,7 +40135,7 @@
         <v>34</v>
       </c>
       <c r="BL76" t="n">
-        <v>1782575585808</v>
+        <v>1782578992387</v>
       </c>
       <c r="BM76" t="n">
         <v>2369.021</v>
@@ -40604,7 +40604,7 @@
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 17238, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AzKmhYPZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/aqmElclx/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2351.05, "sourceLowPrice": 2342.424}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 17238, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/AzKmhYPZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/aqmElclx/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2351.05, "sourceLowPrice": 2342.424, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
@@ -40659,7 +40659,7 @@
         <v>34</v>
       </c>
       <c r="BL77" t="n">
-        <v>1782575585809</v>
+        <v>1782578992387</v>
       </c>
       <c r="BM77" t="n">
         <v>2354.824</v>
@@ -41128,7 +41128,7 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28644, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/oBTwB2OL/", "exitScreenshotUrl": "https://www.tradingview.com/x/w9TI27Un/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2315.551, "sourceLowPrice": 2306.618}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28644, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/oBTwB2OL/", "exitScreenshotUrl": "https://www.tradingview.com/x/w9TI27Un/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2315.551, "sourceLowPrice": 2306.618, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
@@ -41183,7 +41183,7 @@
         <v>34</v>
       </c>
       <c r="BL78" t="n">
-        <v>1782575585809</v>
+        <v>1782578992388</v>
       </c>
       <c r="BM78" t="n">
         <v>2317.824</v>
@@ -41652,7 +41652,7 @@
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 18551, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/gpW9dZTu/", "exitScreenshotUrl": "https://www.tradingview.com/x/Gv1UqXw0/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2310.08, "sourceLowPrice": 2304.8}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 18551, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/gpW9dZTu/", "exitScreenshotUrl": "https://www.tradingview.com/x/Gv1UqXw0/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2310.08, "sourceLowPrice": 2304.8, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
@@ -41707,7 +41707,7 @@
         <v>34</v>
       </c>
       <c r="BL79" t="n">
-        <v>1782575585809</v>
+        <v>1782578992388</v>
       </c>
       <c r="BM79" t="n">
         <v>2313.241</v>
@@ -42176,7 +42176,7 @@
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 21659, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qFIEHlKX/", "exitScreenshotUrl": "https://www.tradingview.com/x/Vj90lc2D/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2307.14, "sourceLowPrice": 2302.948}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 21659, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qFIEHlKX/", "exitScreenshotUrl": "https://www.tradingview.com/x/Vj90lc2D/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2307.14, "sourceLowPrice": 2302.948, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
@@ -42231,7 +42231,7 @@
         <v>34</v>
       </c>
       <c r="BL80" t="n">
-        <v>1782575585809</v>
+        <v>1782578992388</v>
       </c>
       <c r="BM80" t="n">
         <v>2309.814</v>
@@ -42700,7 +42700,7 @@
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 22072, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/VZY4fThQ/", "exitScreenshotUrl": "https://www.tradingview.com/x/i54J1LLH/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2307.832, "sourceLowPrice": 2305.312}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 22072, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/VZY4fThQ/", "exitScreenshotUrl": "https://www.tradingview.com/x/i54J1LLH/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2307.832, "sourceLowPrice": 2305.312, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
@@ -42755,7 +42755,7 @@
         <v>34</v>
       </c>
       <c r="BL81" t="n">
-        <v>1782575585810</v>
+        <v>1782578992388</v>
       </c>
       <c r="BM81" t="n">
         <v>2305.312</v>
@@ -43224,7 +43224,7 @@
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28645, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/d4ygHVMv/", "exitScreenshotUrl": "https://www.tradingview.com/x/6zAuTNCD/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2313.0, "sourceLowPrice": 2307.7}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28645, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/d4ygHVMv/", "exitScreenshotUrl": "https://www.tradingview.com/x/6zAuTNCD/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2313.0, "sourceLowPrice": 2307.7, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
@@ -43279,7 +43279,7 @@
         <v>34</v>
       </c>
       <c r="BL82" t="n">
-        <v>1782575585810</v>
+        <v>1782578992388</v>
       </c>
       <c r="BM82" t="n">
         <v>2306.069</v>
@@ -43748,7 +43748,7 @@
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 22216, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/nDpUf1Ab/", "exitScreenshotUrl": "https://www.tradingview.com/x/Digg8wjv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2307.76, "sourceLowPrice": 2304.5}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 22216, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/nDpUf1Ab/", "exitScreenshotUrl": "https://www.tradingview.com/x/Digg8wjv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2307.76, "sourceLowPrice": 2304.5, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
@@ -43803,7 +43803,7 @@
         <v>34</v>
       </c>
       <c r="BL83" t="n">
-        <v>1782575585811</v>
+        <v>1782578992388</v>
       </c>
       <c r="BM83" t="n">
         <v>2303.447</v>
@@ -44272,7 +44272,7 @@
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 22790, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/w0A8BEBv/", "exitScreenshotUrl": "https://www.tradingview.com/x/y4FnXweb/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2314.38, "sourceLowPrice": 2310.5}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 22790, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/w0A8BEBv/", "exitScreenshotUrl": "https://www.tradingview.com/x/y4FnXweb/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2314.38, "sourceLowPrice": 2310.5, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
@@ -44327,7 +44327,7 @@
         <v>34</v>
       </c>
       <c r="BL84" t="n">
-        <v>1782575585811</v>
+        <v>1782578992388</v>
       </c>
       <c r="BM84" t="n">
         <v>2313.09</v>
@@ -44796,7 +44796,7 @@
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28730, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/yDZImHkS/", "exitScreenshotUrl": "https://www.tradingview.com/x/2oOrAucd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2312.39, "sourceLowPrice": 2306.675}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28730, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/yDZImHkS/", "exitScreenshotUrl": "https://www.tradingview.com/x/2oOrAucd/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2312.39, "sourceLowPrice": 2306.675, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
@@ -44851,7 +44851,7 @@
         <v>34</v>
       </c>
       <c r="BL85" t="n">
-        <v>1782575585811</v>
+        <v>1782578992389</v>
       </c>
       <c r="BM85" t="n">
         <v>2312.522</v>
@@ -45320,7 +45320,7 @@
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28692, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/mysHW1IT/", "exitScreenshotUrl": "https://www.tradingview.com/x/TwpFvksy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2315.75, "sourceLowPrice": 2312.688}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28692, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/mysHW1IT/", "exitScreenshotUrl": "https://www.tradingview.com/x/TwpFvksy/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2315.75, "sourceLowPrice": 2312.688, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
@@ -45375,7 +45375,7 @@
         <v>34</v>
       </c>
       <c r="BL86" t="n">
-        <v>1782575585812</v>
+        <v>1782578992389</v>
       </c>
       <c r="BM86" t="n">
         <v>2313.406</v>
@@ -45556,11 +45556,11 @@
       </c>
       <c r="DL86" t="inlineStr">
         <is>
-          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "hadier 5.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN86" t="inlineStr">
         <is>
@@ -45634,12 +45634,12 @@
       </c>
       <c r="EF86" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG86" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "revenge", "label": "Revenge Trading", "source": "manual", "state": "confirmed", "cost_R": 1.0, "cost_$": 1000, "evidence": "Increased aggression after a prior loss in the session.", "detected_at": "2024-06-12T04:16:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH86" t="inlineStr">
@@ -45844,7 +45844,7 @@
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28731, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/tP5qz7XH/", "exitScreenshotUrl": "https://www.tradingview.com/x/TL4BxDiC/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2337.18, "sourceLowPrice": 2329.5}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28731, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/tP5qz7XH/", "exitScreenshotUrl": "https://www.tradingview.com/x/TL4BxDiC/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2337.18, "sourceLowPrice": 2329.5, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
@@ -45899,7 +45899,7 @@
         <v>34</v>
       </c>
       <c r="BL87" t="n">
-        <v>1782575585812</v>
+        <v>1782578992389</v>
       </c>
       <c r="BM87" t="n">
         <v>2327.212</v>
@@ -46368,7 +46368,7 @@
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 28734, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/hp3pCnfw/", "exitScreenshotUrl": "https://www.tradingview.com/x/z4RO2lfq/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2315.91, "sourceLowPrice": 2308.962}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 28734, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/hp3pCnfw/", "exitScreenshotUrl": "https://www.tradingview.com/x/z4RO2lfq/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2315.91, "sourceLowPrice": 2308.962, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
@@ -46423,7 +46423,7 @@
         <v>34</v>
       </c>
       <c r="BL88" t="n">
-        <v>1782575585812</v>
+        <v>1782578992389</v>
       </c>
       <c r="BM88" t="n">
         <v>2311.398</v>
@@ -46892,7 +46892,7 @@
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 26781, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/hsMsS3pG/", "exitScreenshotUrl": "https://www.tradingview.com/x/uAzeiqIO/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2321.72, "sourceLowPrice": 2316.697}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 26781, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/hsMsS3pG/", "exitScreenshotUrl": "https://www.tradingview.com/x/uAzeiqIO/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2321.72, "sourceLowPrice": 2316.697, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
@@ -46947,7 +46947,7 @@
         <v>34</v>
       </c>
       <c r="BL89" t="n">
-        <v>1782575585813</v>
+        <v>1782578992389</v>
       </c>
       <c r="BM89" t="n">
         <v>2314.485</v>
@@ -47416,7 +47416,7 @@
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 1306, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/QCqpCXux/", "exitScreenshotUrl": "https://www.tradingview.com/x/2fJBAnIr/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2322.66, "sourceLowPrice": 2319.0}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 1306, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/QCqpCXux/", "exitScreenshotUrl": "https://www.tradingview.com/x/2fJBAnIr/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2322.66, "sourceLowPrice": 2319.0, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
@@ -47471,7 +47471,7 @@
         <v>34</v>
       </c>
       <c r="BL90" t="n">
-        <v>1782575585813</v>
+        <v>1782578992389</v>
       </c>
       <c r="BM90" t="n">
         <v>2319.546</v>
@@ -47665,7 +47665,7 @@
       </c>
       <c r="DO90" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 2319.546, "new": 2319.182, "at": 1718599860000}]</t>
         </is>
       </c>
       <c r="DP90" t="n">
@@ -47940,7 +47940,7 @@
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 26057, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/opk8j7ki/", "exitScreenshotUrl": "https://www.tradingview.com/x/jUnkSGll/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2327.64, "sourceLowPrice": 2321.8}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 26057, "mentorFile": "hadier 5.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/opk8j7ki/", "exitScreenshotUrl": "https://www.tradingview.com/x/jUnkSGll/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2327.64, "sourceLowPrice": 2321.8, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
@@ -47995,7 +47995,7 @@
         <v>34</v>
       </c>
       <c r="BL91" t="n">
-        <v>1782575585813</v>
+        <v>1782578992389</v>
       </c>
       <c r="BM91" t="n">
         <v>2323.108</v>
@@ -48189,7 +48189,7 @@
       </c>
       <c r="DO91" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 2323.108, "new": 2322.478, "at": 1718620140000}]</t>
         </is>
       </c>
       <c r="DP91" t="n">
